--- a/docs/xlsx/jobs-2026-10-07.xlsx
+++ b/docs/xlsx/jobs-2026-10-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="735">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,327 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Adventure Tour Guide</t>
+  </si>
+  <si>
+    <t>Door County Adventure Center</t>
+  </si>
+  <si>
+    <t>Sturgeon Bay, WI</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>Hourly</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-adventure-tour-guide-sturgeon-bay-wisconsin/2363013726</t>
+  </si>
+  <si>
+    <t>Annual Giving and Membership Engagement Manager</t>
+  </si>
+  <si>
+    <t>NH Audubon</t>
+  </si>
+  <si>
+    <t>Concord, NH</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$24 - $28 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-annual-giving-and-membership-engagement-manager-concord-new-hampshire/5157609047</t>
+  </si>
+  <si>
+    <t>Boardman Restoration Technician</t>
+  </si>
+  <si>
+    <t>Ecostudies Institute</t>
+  </si>
+  <si>
+    <t>Boardman, OR</t>
+  </si>
+  <si>
+    <t>$21.57 - $23.40 per hour</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-boardman-restoration-technician-boardman-oregon/1207064513</t>
+  </si>
+  <si>
+    <t>Camp Helen Brachman Adventure Activities Manager</t>
+  </si>
+  <si>
+    <t>COA Camp Helen Brachman</t>
+  </si>
+  <si>
+    <t>Almond, WI</t>
+  </si>
+  <si>
+    <t>$600 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-camp-helen-brachman-adventure-activities-manager-almond-wisconsin/7486464320</t>
+  </si>
+  <si>
+    <t>Camp Helen Brachman Aquatic Activities Manager Summer Only</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-camp-helen-brachman-aquatic-activities-manager-summer-only-almond-wisconsin/7688335300</t>
+  </si>
+  <si>
+    <t>Camp Helen Brachman Overnight Camp Counselor Summer Only</t>
+  </si>
+  <si>
+    <t>$450 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-camp-helen-brachman-overnight-camp-counselor--summer-only-almond-wisconsin/5519521899</t>
+  </si>
+  <si>
+    <t>Chief Conservation Officer</t>
+  </si>
+  <si>
+    <t>Ocean Conservancy</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>$280,000 - $350,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-marine-biology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-chief-conservation-officer-washington-dc/9029976194</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>Wildlife Conservation Network</t>
+  </si>
+  <si>
+    <t>San Francisco, CA</t>
+  </si>
+  <si>
+    <t>$210,000 - $240,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-chief-operating-officer-san-francisco-california/9421986638</t>
+  </si>
+  <si>
+    <t>Community Conservation Coordinator – Gabon</t>
+  </si>
+  <si>
+    <t>Wild Conservation Society</t>
+  </si>
+  <si>
+    <t>Libreville, Africa</t>
+  </si>
+  <si>
+    <t>Competitive Salary commensurate with Experience</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-conservation-coordinator--gabon-libreville-africa/5763864299</t>
+  </si>
+  <si>
+    <t>Community Fundraising Manager</t>
+  </si>
+  <si>
+    <t>Conservation Colorado</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>$80,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-fundraising-manager-denver-colorado/6897645367</t>
+  </si>
+  <si>
+    <t>Conifer Nursery Shipping Lead (Grenada Forestry Nursery)</t>
+  </si>
+  <si>
+    <t>Sierra Pacific Industries</t>
+  </si>
+  <si>
+    <t>Grenada, CA</t>
+  </si>
+  <si>
+    <t>$28.50 per hour</t>
+  </si>
+  <si>
+    <t>forestry-admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conifer-nursery-shipping-lead-grenada-forestry-nursery-grenada-california/6552963486</t>
+  </si>
+  <si>
+    <t>Conifer Nursery Shipping Support (Grenada Forestry Nursery)</t>
+  </si>
+  <si>
+    <t>$25.46 per hour</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conifer-nursery-shipping-support-grenada-forestry-nursery-grenada-california/4629125592</t>
+  </si>
+  <si>
+    <t>Conservation Corps New Mexico- 2027 Veterans Fire Corps Crew Member - AmeriCorps</t>
+  </si>
+  <si>
+    <t>Conservation Corps New Mexico</t>
+  </si>
+  <si>
+    <t>Las Cruces, NM</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>Living Allowance of $500 per week Additional Benefit of $400 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-corps-new-mexico--2027veterans-fire-corps-crew-member---americorps-las-cruces-new-mexico/1657600631</t>
+  </si>
+  <si>
+    <t>Deputy Director, Strategy &amp; Operations</t>
+  </si>
+  <si>
+    <t>The Nature Conservancy</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>$112,000 - $137,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-deputy-director-strategy--operations-philadelphia-pennsylvania/1326155537</t>
+  </si>
+  <si>
+    <t>Director of Advancement</t>
+  </si>
+  <si>
+    <t>North County Land Trust</t>
+  </si>
+  <si>
+    <t>Leominster, MA</t>
+  </si>
+  <si>
+    <t>$68,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-advancement-leominster-massachusetts/5585245485</t>
+  </si>
+  <si>
+    <t>Education Coordinator</t>
+  </si>
+  <si>
+    <t>Missouri River Relief</t>
+  </si>
+  <si>
+    <t>Columbia, MO</t>
+  </si>
+  <si>
+    <t>$41,000 - $45,000 per year</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education-coordinator-columbia-missouri/5155744577</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Upper Saranac Foundation</t>
+  </si>
+  <si>
+    <t>Saranac Lake, NY</t>
+  </si>
+  <si>
+    <t>$100,000 - $120,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-sunnyside-new-york/4282363594</t>
+  </si>
+  <si>
+    <t>Worthy Garden Club</t>
+  </si>
+  <si>
+    <t>Bend, OR</t>
+  </si>
+  <si>
+    <t>$80,000 - $120,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-bend-oregon/6911990021</t>
+  </si>
+  <si>
+    <t>Fisheries Disaster Program Analyst</t>
+  </si>
+  <si>
+    <t>A.I.S. Inc.</t>
+  </si>
+  <si>
+    <t>N. Dartmouth, MA</t>
+  </si>
+  <si>
+    <t>$30 - $35 per hour</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-disaster-program-analyst-n-dartmouth-massachusetts/9189293014</t>
+  </si>
+  <si>
+    <t>Fishery Pathologist</t>
+  </si>
+  <si>
+    <t>Idaho Department of Fish and Game</t>
+  </si>
+  <si>
+    <t>Boise, ID</t>
+  </si>
+  <si>
+    <t>$28.94 - $36.17 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fishery-pathologist-boise-idaho/6841095276</t>
+  </si>
+  <si>
     <t>Forestry Technician</t>
   </si>
   <si>
@@ -49,9 +370,6 @@
     <t>Elgin, MN</t>
   </si>
   <si>
-    <t>Permanent</t>
-  </si>
-  <si>
     <t>$18.00/hr</t>
   </si>
   <si>
@@ -61,6 +379,180 @@
     <t>https://www.conservationjobboard.com/job-listing-forestry-technician-elgin-minnesota/9935998127</t>
   </si>
   <si>
+    <t>Forestry Technician (River Ranger)</t>
+  </si>
+  <si>
+    <t>Utah Division of Forestry, Fire, &amp; State Lands</t>
+  </si>
+  <si>
+    <t>Moab, UT</t>
+  </si>
+  <si>
+    <t>$15.09 - $28.16 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-technician-river-ranger-moab-utah/3962863487</t>
+  </si>
+  <si>
+    <t>Lead Observer Coordinator - New England</t>
+  </si>
+  <si>
+    <t>$50,000 - $63,500 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-lead-observer-coordinator---new-england-n-dartmouth-massachusetts/4229492029</t>
+  </si>
+  <si>
+    <t>Manager V (Inland Fisheries Regional Director)</t>
+  </si>
+  <si>
+    <t>Texas Parks &amp; Wildlife Department</t>
+  </si>
+  <si>
+    <t>Waco, TX</t>
+  </si>
+  <si>
+    <t>$10,000 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-manager-v-inland-fisheries-regional-director-waco-texas/6768891485</t>
+  </si>
+  <si>
+    <t>Natural Resources Forestry Specialist</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Natural Resources, Division of Forestry</t>
+  </si>
+  <si>
+    <t>Multiple Locations, MN</t>
+  </si>
+  <si>
+    <t>$25.22 – $36.59 hourly / $52,659 - $76,400 annually</t>
+  </si>
+  <si>
+    <t>ecology-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-forestry-specialist-multiple-locations-minnesota/3135661524</t>
+  </si>
+  <si>
+    <t>Natural Resources Specialist I - II - III (Wildlife District 7 Biologist)</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife Department</t>
+  </si>
+  <si>
+    <t>Jefferson, TX</t>
+  </si>
+  <si>
+    <t>$4,504.18 - $5,824.14 per month</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-specialist-i---ii---iii-wildlife-district-7-biologist-jefferson-texas/4961326538</t>
+  </si>
+  <si>
+    <t>Nursery Manager - Sequoia and Kings Canyon National Parks</t>
+  </si>
+  <si>
+    <t>Sierra Institute for Community and Environment</t>
+  </si>
+  <si>
+    <t>Taylorsville, CA</t>
+  </si>
+  <si>
+    <t>$57,500 - $61,000 per year</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nursery-manager---sequoia-and-kings-canyon-national-parks-taylorsville-california/1115413400</t>
+  </si>
+  <si>
+    <t>Pigeon Point Outdoor Educator</t>
+  </si>
+  <si>
+    <t>Exploring New Horizons Outdoor Schools</t>
+  </si>
+  <si>
+    <t>Pescadero, CA</t>
+  </si>
+  <si>
+    <t>$26 - $31 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-pigeon-point-outdoor-educaotr-pescadero-california/3425452358</t>
+  </si>
+  <si>
+    <t>Presales Forester, Natural Resource Specialist</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Sedro-Woolley, WA</t>
+  </si>
+  <si>
+    <t>$4,004 - $6,075 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-presales-forester-natural-resource-specialist-sedro-woolley-washington/9098636724</t>
+  </si>
+  <si>
+    <t>Property Assistant – Seasonal (Summer-fall)</t>
+  </si>
+  <si>
+    <t>$17.50 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-property-assistant--seasonal-summer-fall-almond-wisconsin/6877997036</t>
+  </si>
+  <si>
+    <t>Research Technician II</t>
+  </si>
+  <si>
+    <t>UGA Marine Institute on Sapelo Island (UGAMI)</t>
+  </si>
+  <si>
+    <t>Sapelo Island, GA</t>
+  </si>
+  <si>
+    <t>Annual salary is minimum $35200. Salary is commensurate with experience.</t>
+  </si>
+  <si>
+    <t>ecology-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-technician-ii-sapelo-island-georgia/4729340447</t>
+  </si>
+  <si>
+    <t>Resilient Indiana Conservation Technician</t>
+  </si>
+  <si>
+    <t>Indiana Association of Soil &amp; Water Conservation Districts</t>
+  </si>
+  <si>
+    <t>Various, IN</t>
+  </si>
+  <si>
+    <t>$51,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-resilient-indiana-conservation-technician-various-indiana/7479399020</t>
+  </si>
+  <si>
     <t>Resource Development Project Coordinator</t>
   </si>
   <si>
@@ -79,6 +571,48 @@
     <t>https://www.conservationjobboard.com/job-listing-resource-development-project-coordinator-monterey-california/3134152414</t>
   </si>
   <si>
+    <t>Sempervirens Outdoor Educator</t>
+  </si>
+  <si>
+    <t>Scotts Valley, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sempervirens-outdoor-educator-scotts-valley-california/8643446875</t>
+  </si>
+  <si>
+    <t>Shorebird Predation Management Biologist</t>
+  </si>
+  <si>
+    <t>Florida Fish and Wildlife Conservation Commission</t>
+  </si>
+  <si>
+    <t>Panama City, FL</t>
+  </si>
+  <si>
+    <t>$21.63 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-shorebird-predation-management-biologist-panama-city-florida/3871957669</t>
+  </si>
+  <si>
+    <t>Spring Term Animal Care Internship</t>
+  </si>
+  <si>
+    <t>The Bishop Museum of Science and Nature</t>
+  </si>
+  <si>
+    <t>Bradenton, FL</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>Unpaid Internship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-spring-term-animal-care-internship-bradenton-florida/2895005475</t>
+  </si>
+  <si>
     <t>Trail Operations Specialist (Roanoke, VA)</t>
   </si>
   <si>
@@ -88,9 +622,6 @@
     <t>Roanoke, VA</t>
   </si>
   <si>
-    <t>Temporary</t>
-  </si>
-  <si>
     <t>$22 - $24 per hour</t>
   </si>
   <si>
@@ -100,6 +631,54 @@
     <t>https://www.conservationjobboard.com/job-listing-trail-operations-specialist-roanoke-va-roanoke-virginia/5664881101</t>
   </si>
   <si>
+    <t>Waste Diversion Technician</t>
+  </si>
+  <si>
+    <t>Town of Erie</t>
+  </si>
+  <si>
+    <t>Erie, CO</t>
+  </si>
+  <si>
+    <t>$22.05 - $27.56 per hour</t>
+  </si>
+  <si>
+    <t>sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-waste-diversion-technician-erie-colorado/7308592730</t>
+  </si>
+  <si>
+    <t>Wild Turkey Field Technicians – Illinois</t>
+  </si>
+  <si>
+    <t>Southern Illinois University – Carbondale</t>
+  </si>
+  <si>
+    <t>Carbondale, IL</t>
+  </si>
+  <si>
+    <t>$18 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wild-turkey-field-technicians--illinois-carbondale-illinois/6700896151</t>
+  </si>
+  <si>
+    <t>Work Planner</t>
+  </si>
+  <si>
+    <t>ArborMetrics</t>
+  </si>
+  <si>
+    <t>Flint, MI</t>
+  </si>
+  <si>
+    <t>$23 - $26 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-work-planner-flint-michigan/3959272502</t>
+  </si>
+  <si>
     <t>Wyoming Conservation Manager</t>
   </si>
   <si>
@@ -116,6 +695,1530 @@
   </si>
   <si>
     <t>https://www.conservationjobboard.com/job-listing-wyoming-conservation-manager-jackson-lander-ft-washakie-or-cody-wyoming/5790286193</t>
+  </si>
+  <si>
+    <t>Southeastern States Conservation Manager</t>
+  </si>
+  <si>
+    <t>The Wilderness Society</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>60,000 - 80,000</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>Idealist</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/southeastern-states-conservation-manager/</t>
+  </si>
+  <si>
+    <t>Account Director</t>
+  </si>
+  <si>
+    <t>BWF Zuri</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/82e0c67d9df64255859e7f4d0da2dab8-account-director-bwf-zuri-bend</t>
+  </si>
+  <si>
+    <t>Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>SAADA</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Race Ethnicity, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f3f96f67faff4e4c93eabbd5580de0ff-administrative-coordinator-saada-philadelphia</t>
+  </si>
+  <si>
+    <t>Annual Giving and Digital Marketing Coordinator II</t>
+  </si>
+  <si>
+    <t>USD 59000.00 - 59000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/468c8266b8024dffaaeab79cacb220fa-annual-giving-and-digital-marketing-coordinator-ii-bwf-zuri-bend</t>
+  </si>
+  <si>
+    <t>Assistant Archivist</t>
+  </si>
+  <si>
+    <t>The Felician Sisters of North America</t>
+  </si>
+  <si>
+    <t>Livonia, Michigan</t>
+  </si>
+  <si>
+    <t>USD 30.25 - 40.91/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/498032b176a042329905fc8fcb675487-assistant-archivist-the-felician-sisters-of-north-america-livonia</t>
+  </si>
+  <si>
+    <t>Associate Attorney, Community Partnerships Program</t>
+  </si>
+  <si>
+    <t>Earthjustice</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 108200.00 - 120700.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5454244028994bad9e01e0e367de5a12-associate-attorney-community-partnerships-program-earthjustice-los-angeles</t>
+  </si>
+  <si>
+    <t>Associate, Strategic Services</t>
+  </si>
+  <si>
+    <t>Aperio Philanthropy</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/1efbfa4e7ad54c0d960277ff55ac02ab-associate-strategic-services-aperio-philanthropy-brooklyn</t>
+  </si>
+  <si>
+    <t>Attorney: Education Team</t>
+  </si>
+  <si>
+    <t>Disability Rights MD</t>
+  </si>
+  <si>
+    <t>Baltimore, MD</t>
+  </si>
+  <si>
+    <t>USD 72100.00 - 77003.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/836a694d4253432da1b6a676888ec0a6-attorney-education-team-disability-rights-md-baltimore</t>
+  </si>
+  <si>
+    <t>Bilingual (English/Spanish) Immigration Program Specialist</t>
+  </si>
+  <si>
+    <t>Masa</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>Urban Areas, Immigrants Or Refugees, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b84f4518a94342ffad0d2c905b27f103-bilingual-englishspanish-immigration-program-specialist-masa-bronx</t>
+  </si>
+  <si>
+    <t>Business Systems and AI Engineer</t>
+  </si>
+  <si>
+    <t>Alfred P. Sloan Foundation</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 155000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f74488e68a154b1aa8e1e641f3d1dc38-business-systems-and-ai-engineer-alfred-p-sloan-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Career Success Coordinator</t>
+  </si>
+  <si>
+    <t>Ed Snider Youth Hockey &amp; Education</t>
+  </si>
+  <si>
+    <t>Children Youth, Sports Recreation, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34f5c554e54744b58ad79a2c7b068908-career-success-coordinator-ed-snider-youth-hockey-education-philadelphia</t>
+  </si>
+  <si>
+    <t>Chief Development Officer</t>
+  </si>
+  <si>
+    <t>Glen Echo Park Partnership for Arts and Culture, Inc.</t>
+  </si>
+  <si>
+    <t>Glen Echo, Maryland</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f40f27a1aa0f49d2899b99107b323a6c-chief-development-officer-glen-echo-park-partnership-for-arts-and-culture-inc-glen-echo</t>
+  </si>
+  <si>
+    <t>Chief Marketing &amp; Sales Officer</t>
+  </si>
+  <si>
+    <t>American Speech-Language-Hearing Association</t>
+  </si>
+  <si>
+    <t>Rockville, MD</t>
+  </si>
+  <si>
+    <t>USD 194277.00 - 216974.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29b9e033e38f42fda6b202150d07ddfa-chief-marketing-sales-officer-american-speech-language-hearing-association-rockville</t>
+  </si>
+  <si>
+    <t>Chinese - Community Navigator</t>
+  </si>
+  <si>
+    <t>Vision Urbana, Inc.</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Hunger Food Security, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a54981ad05514c4798498657bd8e34b7-chinese-community-navigator-vision-urbana-inc-new-york</t>
+  </si>
+  <si>
+    <t>Client Engagement Administrator</t>
+  </si>
+  <si>
+    <t>NPAG</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/41d1f849526a41c3926d94a6aed19c25-client-engagement-administrator-npag-beaverton</t>
+  </si>
+  <si>
+    <t>Clinical Monitor</t>
+  </si>
+  <si>
+    <t>Equip for Equality</t>
+  </si>
+  <si>
+    <t>Remote (Illinois)</t>
+  </si>
+  <si>
+    <t>USD 60270.00 - 72500.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96ee193b93484f01ac562d3ad75108a8-clinical-monitor-equip-for-equality-chicago</t>
+  </si>
+  <si>
+    <t>College and Career Advisor</t>
+  </si>
+  <si>
+    <t>Comprehensive Youth Development</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/683c74f1249f4e7fbf60349e79ef4d1f-college-and-career-advisor-comprehensive-youth-development-new-york</t>
+  </si>
+  <si>
+    <t>College Assistant (Part Time) - Hunter College School of Education | Office of Clinical Experiences</t>
+  </si>
+  <si>
+    <t>Hunter College School of Education</t>
+  </si>
+  <si>
+    <t>USD 19.10 - 19.10/hour</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/caf20a19e1df4f91b299e50e8cb84193-college-assistant-part-time-hunter-college-school-of-education-office-of-clinical-experiences-hunter-college-school-of-education-new-york</t>
+  </si>
+  <si>
+    <t>Communications Associate</t>
+  </si>
+  <si>
+    <t>Borderlands Restoration Network</t>
+  </si>
+  <si>
+    <t>Patagonia, Arizona</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4bb8d413fd44f338fb07d0a13085c6c-communications-associate-borderlands-restoration-network-patagonia</t>
+  </si>
+  <si>
+    <t>Community Economic Development Manager</t>
+  </si>
+  <si>
+    <t>Northwest Side Community Development Corporation</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/864e8bfb8e814328aecb833c159465aa-community-economic-development-manager-northwest-side-community-development-corporation-chicago</t>
+  </si>
+  <si>
+    <t>Community Service Coordinator and Custodian of Building &amp; Grounds</t>
+  </si>
+  <si>
+    <t>First United Methodist Church of Lombard and Villa Park</t>
+  </si>
+  <si>
+    <t>Lombard, Illinois</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Prison Reform, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/55d980ffefb546b887fbdbd40da11b15-community-service-coordinator-and-custodian-of-building-grounds-first-united-methodist-church-of-lombard-and-villa-park-lombard</t>
+  </si>
+  <si>
+    <t>Congregational Engagement Administrator</t>
+  </si>
+  <si>
+    <t>CLF - Church of the Larger Fellowship, Unitarian Universalist</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0952ccfbd8274ac290343ed9e25c05d9-congregational-engagement-administrator-clf-church-of-the-larger-fellowship-unitarian-universalist-boston</t>
+  </si>
+  <si>
+    <t>Conservation Project Manager – Mount Desert Island</t>
+  </si>
+  <si>
+    <t>Maine Coast Heritage Trust</t>
+  </si>
+  <si>
+    <t>Mount Desert, Maine</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2fc76cdc59f74d23ab25eb66288480db-conservation-project-manager-mount-desert-island-maine-coast-heritage-trust-mount-desert</t>
+  </si>
+  <si>
+    <t>Crisis Response Counselor</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Columbia, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45cd191bc08d4711a62e3a7a0eaa5fe1-crisis-response-counselor-youth-villages-columbia</t>
+  </si>
+  <si>
+    <t>Cookeville, Tennessee</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2472af08924742b0baa371ab200990d7-crisis-response-counselor-youth-villages-cookeville</t>
+  </si>
+  <si>
+    <t>CRM System Administrator</t>
+  </si>
+  <si>
+    <t>Reinvestment Partners</t>
+  </si>
+  <si>
+    <t>Durham, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Health Medicine, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0d1a838253814170ac22e015731caf87-crm-system-administrator-reinvestment-partners-durham</t>
+  </si>
+  <si>
+    <t>Customer Relations Manager</t>
+  </si>
+  <si>
+    <t>USD 61624.00 - 68471.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/444598fc071c40a8932d3cb75d4f2219-customer-relations-manager-american-speech-language-hearing-association-rockville</t>
+  </si>
+  <si>
+    <t>Deputy Chief Program Officer</t>
+  </si>
+  <si>
+    <t>PROJECT HOSPITALITY - STATEN ISLAND NY</t>
+  </si>
+  <si>
+    <t>Staten Island, NY</t>
+  </si>
+  <si>
+    <t>USD 155000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b3273084a13476c9c7c0b67c3e26759-deputy-chief-program-officer-project-hospitality-staten-island-ny-staten-island</t>
+  </si>
+  <si>
+    <t>Development Director - Posse Bay Area</t>
+  </si>
+  <si>
+    <t>The Posse Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f85b8c53d044909b680166df3e17557-development-director-posse-bay-area-the-posse-foundation-inc-san-francisco</t>
+  </si>
+  <si>
+    <t>Development Director - Posse Los Angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4a7989fc3a3e432bb053bd921fffd772-development-director-posse-los-angeles-the-posse-foundation-inc-los-angeles</t>
+  </si>
+  <si>
+    <t>Digital Coordinator II</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/281768c959364a8780641802e9aedac7-digital-coordinator-ii-bwf-zuri-bend</t>
+  </si>
+  <si>
+    <t>Director of Capital Partnerships</t>
+  </si>
+  <si>
+    <t>Trust Neighborhoods</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/59cab1927c764e879bd73bba6db27923-director-of-capital-partnerships-trust-neighborhoods-kansas-city</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Chinati Foundation</t>
+  </si>
+  <si>
+    <t>Marfa, Texas</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5237b45f23784c07b623ad687d52f0e8-director-of-development-chinati-foundation-marfa</t>
+  </si>
+  <si>
+    <t>Goddard House in Brookline Assisted Living</t>
+  </si>
+  <si>
+    <t>Brookline, MA</t>
+  </si>
+  <si>
+    <t>USD 100000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Seniors Retirement, Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/763064725fbc492ab678455ac4bba4a3-director-of-development-goddard-house-in-brookline-assisted-living-brookline</t>
+  </si>
+  <si>
+    <t>Director of Education</t>
+  </si>
+  <si>
+    <t>Valley Beit Midrash</t>
+  </si>
+  <si>
+    <t>Scottsdale, Arizona</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce3c2c39a5e546d1aa128b6ab320fcaa-director-of-education-valley-beit-midrash-scottsdale</t>
+  </si>
+  <si>
+    <t>Director of Litigation and Special Projects</t>
+  </si>
+  <si>
+    <t>Youth Represent</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 138000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c0ed49e948443e89810ffbfacc8df21-director-of-litigation-and-special-projects-youth-represent-new-york</t>
+  </si>
+  <si>
+    <t>Director, Native Community Finance</t>
+  </si>
+  <si>
+    <t>Rise Economy</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Microfinance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/187ac97290a0459b833e8f29d38249bc-director-native-community-finance-rise-economy-fresno</t>
+  </si>
+  <si>
+    <t>Dual Enrollment Credential and Course Alignment Manager</t>
+  </si>
+  <si>
+    <t>CUNY K-16 Initiatives</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b0ce789239db4b9f9182433c5f93f381-dual-enrollment-credential-and-course-alignment-manager-cuny-k-16-initiatives-new-york</t>
+  </si>
+  <si>
+    <t>Early Childhood Education Program Coordinator (bilingual English/Spanish)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 76000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Urban Areas, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f698301122c646bdb2207c3431560a9c-early-childhood-education-program-coordinator-bilingual-englishspanish-masa-bronx</t>
+  </si>
+  <si>
+    <t>Early Learning Specialist -Bilingual (Spanish/English)</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afd1344b6ae247f0a9760dd0c680054d-early-learning-specialist-bilingual-spanishenglish-masa-bronx</t>
+  </si>
+  <si>
+    <t>Editor, Moldova</t>
+  </si>
+  <si>
+    <t>Organized Crime and Corruption Reporting Project</t>
+  </si>
+  <si>
+    <t>Remote (MD)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/286ee04cec4b4453b924323b89626685-editor-moldova-organized-crime-and-corruption-reporting-project-amsterdam</t>
+  </si>
+  <si>
+    <t>En AMNISTIA INTERNACIONAL buscamos captadores de fondos en vía pública para CABA</t>
+  </si>
+  <si>
+    <t>Amnistía Internacional Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/491a60fd859b433b88dbe8b338b46531-en-amnistia-internacional-buscamos-captadores-de-fondos-en-via-publica-para-caba-amnistia-internacional-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Evening Audiovisual (AV) Technician</t>
+  </si>
+  <si>
+    <t>Meridian International Center</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6a2fd84bc254448a3b14fd04f235caf-evening-audiovisual-av-technician-meridian-international-center-washington</t>
+  </si>
+  <si>
+    <t>Events &amp; Communications Specialist</t>
+  </si>
+  <si>
+    <t>Friends of the Children - Chicago</t>
+  </si>
+  <si>
+    <t>USD 63888.00 - 63888.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65a54bc59c1e4e209b64bf977bbbc19f-events-communications-specialist-friends-of-the-children-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Events Manager</t>
+  </si>
+  <si>
+    <t>Tech Coalition</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Crime Safety, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f07c15f8ac3e4b75a44021cf6635ea91-events-manager-tech-coalition-reston</t>
+  </si>
+  <si>
+    <t>Placer Nature Center</t>
+  </si>
+  <si>
+    <t>Auburn, California</t>
+  </si>
+  <si>
+    <t>USD 26000.00 - 46800.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8cbf8af7cf0b4e529aa989e245279104-executive-director-placer-nature-center-auburn</t>
+  </si>
+  <si>
+    <t>Facilitador/a Educativo/a en CDMX/ Edo. Mex( Virtual)</t>
+  </si>
+  <si>
+    <t>Educación para Compartir - México</t>
+  </si>
+  <si>
+    <t>Remote (Ciudad de México, Ciudad de México, MX)</t>
+  </si>
+  <si>
+    <t>MXN 15000.00 - 15000.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f63897adce041d5844b91d93ba8d988-facilitadora-educativoa-en-cdmx-edo-mex-virtual-educacion-para-compartir-mexico-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Fellow - Consumer Rights &amp; Economic Justice</t>
+  </si>
+  <si>
+    <t>Public Counsel</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a1ea59bd9794f9f9dfdbdf86ee39ec9-fellow-consumer-rights-economic-justice-public-counsel-los-angeles</t>
+  </si>
+  <si>
+    <t>Foster Care Specialist</t>
+  </si>
+  <si>
+    <t>Jackson, Tennessee</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4bf72ef5e05440fa8fda611fcce91942-foster-care-specialist-youth-villages-jackson</t>
+  </si>
+  <si>
+    <t>Grants Manager</t>
+  </si>
+  <si>
+    <t>Commonwealth</t>
+  </si>
+  <si>
+    <t>USD 64000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d344e7cac5f44b7d8448a6a676fa1471-grants-manager-commonwealth-boston</t>
+  </si>
+  <si>
+    <t>Communities In Schools of Los Angeles</t>
+  </si>
+  <si>
+    <t>USD 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e5069cd84fd44bb94558af851497fd8-grants-manager-communities-in-schools-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Housing Case Manager</t>
+  </si>
+  <si>
+    <t>Safe Alternatives to Violent Environments</t>
+  </si>
+  <si>
+    <t>Fremont, California</t>
+  </si>
+  <si>
+    <t>USD 32.86 - 32.86/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/663e4f131f964190866fdd291e5c9d26-housing-case-manager-safe-alternatives-to-violent-environments-fremont</t>
+  </si>
+  <si>
+    <t>International Programs Manager (Bilingual in English &amp; Spanish)</t>
+  </si>
+  <si>
+    <t>Global Strays</t>
+  </si>
+  <si>
+    <t>Animals, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5e700b706c5452fa12471d95e2a6165-international-programs-manager-bilingual-in-english-spanish-global-strays-southampton</t>
+  </si>
+  <si>
+    <t>Investigative Advocate: Representative Payee Team</t>
+  </si>
+  <si>
+    <t>USD 45850.00 - 49890.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1664df9bce44f9fa646046897fc48ec-investigative-advocate-representative-payee-team-disability-rights-md-baltimore</t>
+  </si>
+  <si>
+    <t>Job Placement Manager</t>
+  </si>
+  <si>
+    <t>Emma's Torch</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Hunger Food Security, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d84654e404e345409156c1973fa7a6a6-job-placement-manager-emmas-torch-kings-county</t>
+  </si>
+  <si>
+    <t>Manager of Learning and Development</t>
+  </si>
+  <si>
+    <t>Paul M. Angell Family Foundation (PMAFF)</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc84eabe36f74e24bac02b8c3dc6f981-manager-of-learning-and-development-paul-m-angell-family-foundation-pmaff-chicago</t>
+  </si>
+  <si>
+    <t>Manager of Program Initiatives</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d390d095c8664d5bb49fc35431d6a83e-manager-of-program-initiatives-paul-m-angell-family-foundation-pmaff-chicago</t>
+  </si>
+  <si>
+    <t>Manager of Talent Acquisition, 5-Year Term</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7239b5dadaf14f1988e29619902280b2-manager-of-talent-acquisition-5-year-term-paul-m-angell-family-foundation-pmaff-chicago</t>
+  </si>
+  <si>
+    <t>Manager, Partner Success (Full-Time Position, Hybrid)</t>
+  </si>
+  <si>
+    <t>Cause Strategy Partners</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/e51ab4b233534529a9fcf79a071d335e-manager-partner-success-full-time-position-hybrid-cause-strategy-partners-washington</t>
+  </si>
+  <si>
+    <t>Managing Director, Collaborative Capital</t>
+  </si>
+  <si>
+    <t>GitLab Foundation</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c174920e3f04542827cd277828edbfc-managing-director-collaborative-capital-gitlab-foundation-san-francisco</t>
+  </si>
+  <si>
+    <t>Medical Director in Belize - Live Abroad</t>
+  </si>
+  <si>
+    <t>Hillside Health Care</t>
+  </si>
+  <si>
+    <t>Eldridgeville, Belize, BZ</t>
+  </si>
+  <si>
+    <t>USD 18804.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0424187cab834acc84e210d14f004a81-medical-director-in-belize-live-abroad-hillside-health-care-eldridgeville</t>
+  </si>
+  <si>
+    <t>Member Care Specialist</t>
+  </si>
+  <si>
+    <t>Soroptimist International of the Americas, Inc.</t>
+  </si>
+  <si>
+    <t>USD 34000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e441c11913d4762a8011496615340de-member-care-specialist-soroptimist-international-of-the-americas-inc-philadelphia</t>
+  </si>
+  <si>
+    <t>Mid-Level Giving Officer</t>
+  </si>
+  <si>
+    <t>Environmental Defense Fund</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a048c301eac24f86a2c7ddd40e4caf05-mid-level-giving-officer-environmental-defense-fund-new-york</t>
+  </si>
+  <si>
+    <t>Nurse Manager (Home Care Setting)</t>
+  </si>
+  <si>
+    <t>Maryknoll Sisters</t>
+  </si>
+  <si>
+    <t>Ossining, New York</t>
+  </si>
+  <si>
+    <t>USD 118560.00 - 118560.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b0509768c204f01937385fca020848e-nurse-manager-home-care-setting-maryknoll-sisters-ossining</t>
+  </si>
+  <si>
+    <t>Operations and Membership Manager</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>Policy, Job Workplace, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/6f027615834348a597a437de266a17de-operations-and-membership-manager-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>TSNE</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/471d5ba397bf436dbec55e59aa884b1a-operations-manager-tsne-new-york</t>
+  </si>
+  <si>
+    <t>Outreach, Education &amp; Prevention Specialist</t>
+  </si>
+  <si>
+    <t>Independence House, Inc.</t>
+  </si>
+  <si>
+    <t>Barnstable, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b63b34b0454a4a68ace21ecd282df73d-outreach-education-prevention-specialist-independence-house-inc-barnstable</t>
+  </si>
+  <si>
+    <t>Part-Time Bookkeeper – Nonprofit Fund Accounting</t>
+  </si>
+  <si>
+    <t>Life On Art</t>
+  </si>
+  <si>
+    <t>Petaluma, California</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4950aa414c074bc19da4fcc5767c92fd-part-time-bookkeeper-nonprofit-fund-accounting-life-on-art-petaluma</t>
+  </si>
+  <si>
+    <t>Philanthropic Advisor (San Francisco Bay Area region)</t>
+  </si>
+  <si>
+    <t>Movement Voter Project</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd25f1a698d44891b8010d8cd65255a1-philanthropic-advisor-san-francisco-bay-area-region-movement-voter-project-northampton</t>
+  </si>
+  <si>
+    <t>Policy Coordinator - LPSC &amp; MISO</t>
+  </si>
+  <si>
+    <t>Alliance for Affordable Energy</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Consumer Protection</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3a65893c9684d70bb44b4a7828e23c5-policy-coordinator-lpsc-miso-alliance-for-affordable-energy-new-orleans</t>
+  </si>
+  <si>
+    <t>Policy Project Manager, Retirement</t>
+  </si>
+  <si>
+    <t>American Academy of Actuaries</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2864109b84a4486abb9a58403b14de7-policy-project-manager-retirement-american-academy-of-actuaries-washington</t>
+  </si>
+  <si>
+    <t>Portugal - Early Childhood Educator and a Primary School Teacher</t>
+  </si>
+  <si>
+    <t>O Mundo Somos Nós</t>
+  </si>
+  <si>
+    <t>Vila Verde, Braga, PT</t>
+  </si>
+  <si>
+    <t>EUR 1300.00 - 1300.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9730dec6cb2949a0af138b0338aaa06f-portugal-early-childhood-educator-and-a-primary-school-teacher-o-mundo-somos-nos-vila-verde</t>
+  </si>
+  <si>
+    <t>Primary English and Social Studies Teacher</t>
+  </si>
+  <si>
+    <t>PROEA - Pro Educacion y Ambiente</t>
+  </si>
+  <si>
+    <t>Rincón, Rincón, PR</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2e6c3e7864c04a98a2116ee3f17cb0a2-primary-english-and-social-studies-teacher-proea-pro-educacion-y-ambiente-rincon</t>
+  </si>
+  <si>
+    <t>Primary Science and Math Teacher</t>
+  </si>
+  <si>
+    <t>Education, Environment, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5fa1edb974949e9b6f49d8db9807dd1-primary-science-and-math-teacher-proea-pro-educacion-y-ambiente-rincon</t>
+  </si>
+  <si>
+    <t>Primary Spanish + Arts &amp; Crafts + Environmental Science (outdoor learning)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73e78373ea0c46e48819f9f0f8d57b56-primary-spanish-arts-crafts-environmental-science-outdoor-learning-proea-pro-educacion-y-ambiente-rincon</t>
+  </si>
+  <si>
+    <t>Product Support Specialist</t>
+  </si>
+  <si>
+    <t>FundMiner</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Entrepreneurship, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/c8456ef78c3c49e7addb5bc5d1d93142-product-support-specialist-fundminer-el-paso</t>
+  </si>
+  <si>
+    <t>Program Assistant for Training &amp; Advocacy</t>
+  </si>
+  <si>
+    <t>The Episcopal Church in Connecticut</t>
+  </si>
+  <si>
+    <t>Meriden, Connecticut</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Civic Engagement, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37ee25991d1e46ee9a13c2f462260361-program-assistant-for-training-advocacy-the-episcopal-church-in-connecticut-meriden</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1983c1ff240491aa07d27a9c914bca9-program-manager-life-on-art-petaluma</t>
+  </si>
+  <si>
+    <t>Program Manager - Partnerships</t>
+  </si>
+  <si>
+    <t>PENCIL</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 66000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7f41614746641878495c15ff48fece7-program-manager-partnerships-pencil-new-york</t>
+  </si>
+  <si>
+    <t>Program Specialist-Community Specialist</t>
+  </si>
+  <si>
+    <t>Vermont Foodbank</t>
+  </si>
+  <si>
+    <t>Barre, VT</t>
+  </si>
+  <si>
+    <t>USD 54376.00 - 73568.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Poverty, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60acf6b1efa24ba78c24440567642d08-program-specialist-community-specialist-vermont-foodbank-barre</t>
+  </si>
+  <si>
+    <t>Provincial Sustainability Assistant</t>
+  </si>
+  <si>
+    <t>USD 26.44 - 40.87/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/205e6c6e454f45509d38613df07b520d-provincial-sustainability-assistant-the-felician-sisters-of-north-america-beaver-falls</t>
+  </si>
+  <si>
+    <t>Public Health Director in beautiful Belize</t>
+  </si>
+  <si>
+    <t>Punta Gorda, Toledo District, BZ</t>
+  </si>
+  <si>
+    <t>USD 16000.00 - 18000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b245d74f5cc9409d8e37d9ebf1e75401-public-health-director-in-beautiful-belize-hillside-health-care-punta-gorda</t>
+  </si>
+  <si>
+    <t>Recruitment &amp; Outreach Associate</t>
+  </si>
+  <si>
+    <t>Green City Force</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Energy, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f16d13e31264d039a195cb3aa3ff91b-recruitment-outreach-associate-green-city-force-new-york</t>
+  </si>
+  <si>
+    <t>Refugee School Impact Program Manager</t>
+  </si>
+  <si>
+    <t>School's Out Washington</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 67800.00 - 81400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13d1eae1771e43c78c40b36eceea1ea8-refugee-school-impact-program-manager-schools-out-washington-seattle</t>
+  </si>
+  <si>
+    <t>Safe House Program Assistant - (FT and PT)</t>
+  </si>
+  <si>
+    <t>USD 26.44 - 26.44/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/31544aee6acd433d9e6db09b088de36a-safe-house-program-assistant-ft-and-pt-safe-alternatives-to-violent-environments-fremont</t>
+  </si>
+  <si>
+    <t>Safe House Program Manager</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ca181f016e74323a4e9e1714f059256-safe-house-program-manager-safe-alternatives-to-violent-environments-fremont</t>
+  </si>
+  <si>
+    <t>School Nurse</t>
+  </si>
+  <si>
+    <t>Middle Way School</t>
+  </si>
+  <si>
+    <t>Saugerties, New York</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e865db9304c4737acafc4c10f562091-school-nurse-middle-way-school-saugerties</t>
+  </si>
+  <si>
+    <t>Senior Attorney (Real Estate)</t>
+  </si>
+  <si>
+    <t>New York City School Construction Authority</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 91193.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5edb77c53154ccbb0eb296fbc1136b2-senior-attorney-real-estate-new-york-city-school-construction-authority-queens-county</t>
+  </si>
+  <si>
+    <t>Senior Development Manager</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e835a3f5c584509850a812586e945f7-senior-development-manager-green-city-force-new-york</t>
+  </si>
+  <si>
+    <t>Senior Manager of Education Design</t>
+  </si>
+  <si>
+    <t>The News Literacy Project</t>
+  </si>
+  <si>
+    <t>USD 77500.00 - 82500.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6ea8c77a6624f02a19f1f5016213f31-senior-manager-of-education-design-the-news-literacy-project-washington</t>
+  </si>
+  <si>
+    <t>Senior Manager of Individual Giving</t>
+  </si>
+  <si>
+    <t>Marwen</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75e588ff91594d2283dce858f394239d-senior-manager-of-individual-giving-marwen-chicago</t>
+  </si>
+  <si>
+    <t>Senior Manager, Qualitative Evaluation and Insights</t>
+  </si>
+  <si>
+    <t>Constructive Dialogue Institute</t>
+  </si>
+  <si>
+    <t>USD 101000.00 - 113000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72adaa05f40c419297a2339efd1055d3-senior-manager-qualitative-evaluation-and-insights-constructive-dialogue-institute-new-york</t>
+  </si>
+  <si>
+    <t>Senior Paralegal</t>
+  </si>
+  <si>
+    <t>Asian Law Caucus</t>
+  </si>
+  <si>
+    <t>USD 90270.72 - 101599.92/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26dc887c676c48929bd01f15439d6bf2-senior-paralegal-asian-law-caucus-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Program Manager</t>
+  </si>
+  <si>
+    <t>Reach Incorporated</t>
+  </si>
+  <si>
+    <t>USD 79000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94217cbc0d394471918e9d3060d729ac-senior-program-manager-reach-incorporated-washington</t>
+  </si>
+  <si>
+    <t>Silver Spring Customer Relations Associate Part-Time Position</t>
+  </si>
+  <si>
+    <t>Levine Music</t>
+  </si>
+  <si>
+    <t>Silver Spring, Maryland</t>
+  </si>
+  <si>
+    <t>USD 18.40 - 18.40/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c719c3f6ebf4522a7971e193b4091ed-silver-spring-customer-relations-associate-part-time-position-levine-music-silver-spring</t>
+  </si>
+  <si>
+    <t>Social Worker, Birth Parent Services</t>
+  </si>
+  <si>
+    <t>Spence-Chapin Services to Families and Children</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 71000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a787bbe0dcbe465aabf3a39a845703fe-social-worker-birth-parent-services-spence-chapin-services-to-families-and-children-new-york</t>
+  </si>
+  <si>
+    <t>Green Jobs</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c212da2ff6d48c4974eeb007a05310d-southeastern-states-conservation-manager-the-wilderness-society-washington</t>
+  </si>
+  <si>
+    <t>Speech-Language Pathologist Volunteer</t>
+  </si>
+  <si>
+    <t>Eldridgeville, Toledo District, BZ</t>
+  </si>
+  <si>
+    <t>USD 16000.00 - 18804.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65cd42435550441b9471fa485740d195-speech-language-pathologist-volunteer-hillside-health-care-eldridgeville</t>
+  </si>
+  <si>
+    <t>Staff Attorney - Workers' Rights</t>
+  </si>
+  <si>
+    <t>Legal Aid Bureau, Inc.</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 79116.00 - 122122.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1cd2114608b04d4185a2683a62d3967f-staff-attorney-workers-rights-legal-aid-bureau-inc-baltimore</t>
+  </si>
+  <si>
+    <t>Staff Attorney &amp; Manager, The People's Immigration Clinic</t>
+  </si>
+  <si>
+    <t>Southwest Suburban Immigrant Project</t>
+  </si>
+  <si>
+    <t>Bolingbrook, Illinois</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d76f50d088e44a0ab516d4b8081997c-staff-attorney-manager-the-peoples-immigration-clinic-southwest-suburban-immigrant-project-bolingbrook</t>
+  </si>
+  <si>
+    <t>State Affairs Counsel</t>
+  </si>
+  <si>
+    <t>American Association for Justice</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d46d80b4fd464a90af9254f41113fe62-state-affairs-counsel-american-association-for-justice-washington</t>
+  </si>
+  <si>
+    <t>Student Support Specialist [Willoughby]</t>
+  </si>
+  <si>
+    <t>Replications, Inc</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94d4c1ea037c415ebddbc3a85705bfe9-student-support-specialist-willoughby-replications-inc-brooklyn</t>
+  </si>
+  <si>
+    <t>Summer Fellowship</t>
+  </si>
+  <si>
+    <t>Education Pioneers, Inc.</t>
+  </si>
+  <si>
+    <t>USD 10000.00 - 10000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db6c4bdc68db4d4e9cbb7a0f8169113a-summer-fellowship-education-pioneers-inc-san-francisco</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afd3cd0f384847869d7254c20ab4b528-summer-fellowship-education-pioneers-inc-dallas</t>
+  </si>
+  <si>
+    <t>Teaching Artists - Dance &amp; Music</t>
+  </si>
+  <si>
+    <t>Marquis Studios</t>
+  </si>
+  <si>
+    <t>USD 80.00 - 85.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/426713d96460461cac134cd66c56bfb1-teaching-artists-dance-music-marquis-studios-new-york</t>
+  </si>
+  <si>
+    <t>Youth Counselor (Residential Services) (Full Time and Part-Time Shifts available)</t>
+  </si>
+  <si>
+    <t>Casa de Amparo</t>
+  </si>
+  <si>
+    <t>San Marcos, California</t>
+  </si>
+  <si>
+    <t>USD 22.50 - 22.50/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12367c8b0d20442da2bcfcbf167035fd-youth-counselor-residential-services-full-time-and-part-time-shifts-available-casa-de-amparo-san-marcos</t>
+  </si>
+  <si>
+    <t>Youth Development &amp; Wellness Lead</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2cc3ebe6aa244ec5b0adb3963df6c877-youth-development-wellness-lead-replications-inc-bronx</t>
   </si>
 </sst>
 </file>
@@ -501,7 +2604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -574,30 +2677,30 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
         <v>25</v>
@@ -620,16 +2723,867 @@
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
       </c>
       <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" t="s">
+        <v>97</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" t="s">
+        <v>102</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" t="s">
+        <v>108</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>124</v>
+      </c>
+      <c r="F23" t="s">
+        <v>125</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" t="s">
+        <v>108</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25" t="s">
+        <v>108</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>138</v>
+      </c>
+      <c r="F26" t="s">
+        <v>139</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" t="s">
+        <v>143</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27" t="s">
+        <v>145</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>147</v>
+      </c>
+      <c r="B28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" t="s">
+        <v>151</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F29" t="s">
+        <v>157</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F30" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>164</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" t="s">
+        <v>166</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>168</v>
+      </c>
+      <c r="B32" t="s">
+        <v>169</v>
+      </c>
+      <c r="C32" t="s">
+        <v>170</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>171</v>
+      </c>
+      <c r="F32" t="s">
+        <v>172</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33" t="s">
+        <v>166</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C34" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>182</v>
+      </c>
+      <c r="F34" t="s">
+        <v>183</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B35" t="s">
+        <v>154</v>
+      </c>
+      <c r="C35" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
+        <v>156</v>
+      </c>
+      <c r="F35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" t="s">
+        <v>189</v>
+      </c>
+      <c r="C36" t="s">
+        <v>190</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>191</v>
+      </c>
+      <c r="F36" t="s">
+        <v>145</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37" t="s">
+        <v>195</v>
+      </c>
+      <c r="D37" t="s">
+        <v>196</v>
+      </c>
+      <c r="E37" t="s">
+        <v>197</v>
+      </c>
+      <c r="F37" t="s">
+        <v>145</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>199</v>
+      </c>
+      <c r="B38" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" t="s">
+        <v>201</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>202</v>
+      </c>
+      <c r="F38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>205</v>
+      </c>
+      <c r="B39" t="s">
+        <v>206</v>
+      </c>
+      <c r="C39" t="s">
+        <v>207</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>208</v>
+      </c>
+      <c r="F39" t="s">
+        <v>209</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>211</v>
+      </c>
+      <c r="B40" t="s">
+        <v>212</v>
+      </c>
+      <c r="C40" t="s">
+        <v>213</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>214</v>
+      </c>
+      <c r="F40" t="s">
+        <v>145</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>216</v>
+      </c>
+      <c r="B41" t="s">
+        <v>217</v>
+      </c>
+      <c r="C41" t="s">
+        <v>218</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
+        <v>219</v>
+      </c>
+      <c r="F41" t="s">
+        <v>68</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>221</v>
+      </c>
+      <c r="B42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C42" t="s">
+        <v>223</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s">
+        <v>224</v>
+      </c>
+      <c r="F42" t="s">
+        <v>225</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -639,6 +3593,43 @@
     <hyperlink ref="H3" r:id="rId2"/>
     <hyperlink ref="H4" r:id="rId3"/>
     <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -647,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -686,8 +3677,37 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G2" t="s">
+        <v>233</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -695,7 +3715,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -734,8 +3754,2557 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F3" t="s">
+        <v>246</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F4" t="s">
+        <v>239</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F5" t="s">
+        <v>255</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F7" t="s">
+        <v>266</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B8" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E8" t="s">
+        <v>271</v>
+      </c>
+      <c r="F8" t="s">
+        <v>272</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+      <c r="E9" t="s">
+        <v>278</v>
+      </c>
+      <c r="F9" t="s">
+        <v>279</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>281</v>
+      </c>
+      <c r="B10" t="s">
+        <v>282</v>
+      </c>
+      <c r="C10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D10" t="s">
+        <v>237</v>
+      </c>
+      <c r="E10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F10" t="s">
+        <v>266</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>286</v>
+      </c>
+      <c r="B11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D11" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11" t="s">
+        <v>261</v>
+      </c>
+      <c r="F11" t="s">
+        <v>288</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>290</v>
+      </c>
+      <c r="B12" t="s">
+        <v>291</v>
+      </c>
+      <c r="C12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F12" t="s">
+        <v>294</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>296</v>
+      </c>
+      <c r="B13" t="s">
+        <v>297</v>
+      </c>
+      <c r="C13" t="s">
+        <v>298</v>
+      </c>
+      <c r="D13" t="s">
+        <v>237</v>
+      </c>
+      <c r="E13" t="s">
+        <v>299</v>
+      </c>
+      <c r="F13" t="s">
+        <v>300</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" t="s">
+        <v>303</v>
+      </c>
+      <c r="C14" t="s">
+        <v>283</v>
+      </c>
+      <c r="D14" t="s">
+        <v>277</v>
+      </c>
+      <c r="E14" t="s">
+        <v>304</v>
+      </c>
+      <c r="F14" t="s">
+        <v>305</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>307</v>
+      </c>
+      <c r="B15" t="s">
+        <v>308</v>
+      </c>
+      <c r="C15" t="s">
+        <v>229</v>
+      </c>
+      <c r="D15" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" t="s">
+        <v>309</v>
+      </c>
+      <c r="F15" t="s">
+        <v>261</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B16" t="s">
+        <v>312</v>
+      </c>
+      <c r="C16" t="s">
+        <v>313</v>
+      </c>
+      <c r="D16" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F16" t="s">
+        <v>315</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>317</v>
+      </c>
+      <c r="B17" t="s">
+        <v>318</v>
+      </c>
+      <c r="C17" t="s">
+        <v>283</v>
+      </c>
+      <c r="D17" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" t="s">
+        <v>319</v>
+      </c>
+      <c r="F17" t="s">
+        <v>320</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>322</v>
+      </c>
+      <c r="B18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C18" t="s">
+        <v>283</v>
+      </c>
+      <c r="D18" t="s">
+        <v>244</v>
+      </c>
+      <c r="E18" t="s">
+        <v>324</v>
+      </c>
+      <c r="F18" t="s">
+        <v>325</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>327</v>
+      </c>
+      <c r="B19" t="s">
+        <v>328</v>
+      </c>
+      <c r="C19" t="s">
+        <v>329</v>
+      </c>
+      <c r="D19" t="s">
+        <v>237</v>
+      </c>
+      <c r="E19" t="s">
+        <v>330</v>
+      </c>
+      <c r="F19" t="s">
+        <v>331</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>333</v>
+      </c>
+      <c r="B20" t="s">
+        <v>334</v>
+      </c>
+      <c r="C20" t="s">
+        <v>335</v>
+      </c>
+      <c r="D20" t="s">
+        <v>237</v>
+      </c>
+      <c r="E20" t="s">
+        <v>336</v>
+      </c>
+      <c r="F20" t="s">
+        <v>337</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>339</v>
+      </c>
+      <c r="B21" t="s">
+        <v>340</v>
+      </c>
+      <c r="C21" t="s">
+        <v>341</v>
+      </c>
+      <c r="D21" t="s">
+        <v>244</v>
+      </c>
+      <c r="E21" t="s">
+        <v>342</v>
+      </c>
+      <c r="F21" t="s">
+        <v>343</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>345</v>
+      </c>
+      <c r="B22" t="s">
+        <v>346</v>
+      </c>
+      <c r="C22" t="s">
+        <v>229</v>
+      </c>
+      <c r="D22" t="s">
+        <v>244</v>
+      </c>
+      <c r="E22" t="s">
+        <v>347</v>
+      </c>
+      <c r="F22" t="s">
+        <v>348</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>350</v>
+      </c>
+      <c r="B23" t="s">
+        <v>351</v>
+      </c>
+      <c r="C23" t="s">
+        <v>352</v>
+      </c>
+      <c r="D23" t="s">
+        <v>237</v>
+      </c>
+      <c r="E23" t="s">
+        <v>353</v>
+      </c>
+      <c r="F23" t="s">
+        <v>331</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>355</v>
+      </c>
+      <c r="B24" t="s">
+        <v>356</v>
+      </c>
+      <c r="C24" t="s">
+        <v>357</v>
+      </c>
+      <c r="D24" t="s">
+        <v>237</v>
+      </c>
+      <c r="E24" t="s">
+        <v>358</v>
+      </c>
+      <c r="F24" t="s">
+        <v>359</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>355</v>
+      </c>
+      <c r="B25" t="s">
+        <v>356</v>
+      </c>
+      <c r="C25" t="s">
+        <v>361</v>
+      </c>
+      <c r="D25" t="s">
+        <v>237</v>
+      </c>
+      <c r="E25" t="s">
+        <v>358</v>
+      </c>
+      <c r="F25" t="s">
+        <v>359</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>363</v>
+      </c>
+      <c r="B26" t="s">
+        <v>364</v>
+      </c>
+      <c r="C26" t="s">
+        <v>365</v>
+      </c>
+      <c r="D26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E26" t="s">
+        <v>366</v>
+      </c>
+      <c r="F26" t="s">
+        <v>367</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>369</v>
+      </c>
+      <c r="B27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C27" t="s">
+        <v>298</v>
+      </c>
+      <c r="D27" t="s">
+        <v>237</v>
+      </c>
+      <c r="E27" t="s">
+        <v>370</v>
+      </c>
+      <c r="F27" t="s">
+        <v>261</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>372</v>
+      </c>
+      <c r="B28" t="s">
+        <v>373</v>
+      </c>
+      <c r="C28" t="s">
+        <v>374</v>
+      </c>
+      <c r="D28" t="s">
+        <v>237</v>
+      </c>
+      <c r="E28" t="s">
+        <v>375</v>
+      </c>
+      <c r="F28" t="s">
+        <v>376</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>378</v>
+      </c>
+      <c r="B29" t="s">
+        <v>379</v>
+      </c>
+      <c r="C29" t="s">
+        <v>380</v>
+      </c>
+      <c r="D29" t="s">
+        <v>237</v>
+      </c>
+      <c r="E29" t="s">
+        <v>381</v>
+      </c>
+      <c r="F29" t="s">
+        <v>382</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>384</v>
+      </c>
+      <c r="B30" t="s">
+        <v>379</v>
+      </c>
+      <c r="C30" t="s">
+        <v>259</v>
+      </c>
+      <c r="D30" t="s">
+        <v>237</v>
+      </c>
+      <c r="E30" t="s">
+        <v>381</v>
+      </c>
+      <c r="F30" t="s">
+        <v>382</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>386</v>
+      </c>
+      <c r="B31" t="s">
+        <v>236</v>
+      </c>
+      <c r="C31" t="s">
+        <v>229</v>
+      </c>
+      <c r="D31" t="s">
+        <v>237</v>
+      </c>
+      <c r="E31" t="s">
+        <v>249</v>
+      </c>
+      <c r="F31" t="s">
+        <v>239</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>388</v>
+      </c>
+      <c r="B32" t="s">
+        <v>389</v>
+      </c>
+      <c r="C32" t="s">
+        <v>229</v>
+      </c>
+      <c r="D32" t="s">
+        <v>237</v>
+      </c>
+      <c r="E32" t="s">
+        <v>390</v>
+      </c>
+      <c r="F32" t="s">
+        <v>391</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>393</v>
+      </c>
+      <c r="B33" t="s">
+        <v>394</v>
+      </c>
+      <c r="C33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D33" t="s">
+        <v>237</v>
+      </c>
+      <c r="E33" t="s">
+        <v>396</v>
+      </c>
+      <c r="F33" t="s">
+        <v>294</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>393</v>
+      </c>
+      <c r="B34" t="s">
+        <v>398</v>
+      </c>
+      <c r="C34" t="s">
+        <v>399</v>
+      </c>
+      <c r="D34" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" t="s">
+        <v>400</v>
+      </c>
+      <c r="F34" t="s">
+        <v>401</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>403</v>
+      </c>
+      <c r="B35" t="s">
+        <v>404</v>
+      </c>
+      <c r="C35" t="s">
+        <v>405</v>
+      </c>
+      <c r="D35" t="s">
+        <v>237</v>
+      </c>
+      <c r="E35" t="s">
+        <v>406</v>
+      </c>
+      <c r="F35" t="s">
+        <v>407</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>409</v>
+      </c>
+      <c r="B36" t="s">
+        <v>410</v>
+      </c>
+      <c r="C36" t="s">
+        <v>283</v>
+      </c>
+      <c r="D36" t="s">
+        <v>237</v>
+      </c>
+      <c r="E36" t="s">
+        <v>411</v>
+      </c>
+      <c r="F36" t="s">
+        <v>412</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>414</v>
+      </c>
+      <c r="B37" t="s">
+        <v>415</v>
+      </c>
+      <c r="C37" t="s">
+        <v>416</v>
+      </c>
+      <c r="D37" t="s">
+        <v>237</v>
+      </c>
+      <c r="E37" t="s">
+        <v>293</v>
+      </c>
+      <c r="F37" t="s">
+        <v>417</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>419</v>
+      </c>
+      <c r="B38" t="s">
+        <v>420</v>
+      </c>
+      <c r="C38" t="s">
+        <v>283</v>
+      </c>
+      <c r="D38" t="s">
+        <v>237</v>
+      </c>
+      <c r="E38" t="s">
+        <v>421</v>
+      </c>
+      <c r="F38" t="s">
+        <v>325</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>423</v>
+      </c>
+      <c r="B39" t="s">
+        <v>275</v>
+      </c>
+      <c r="C39" t="s">
+        <v>276</v>
+      </c>
+      <c r="D39" t="s">
+        <v>237</v>
+      </c>
+      <c r="E39" t="s">
+        <v>424</v>
+      </c>
+      <c r="F39" t="s">
+        <v>425</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>427</v>
+      </c>
+      <c r="B40" t="s">
+        <v>275</v>
+      </c>
+      <c r="C40" t="s">
+        <v>276</v>
+      </c>
+      <c r="D40" t="s">
+        <v>237</v>
+      </c>
+      <c r="E40" t="s">
+        <v>428</v>
+      </c>
+      <c r="F40" t="s">
+        <v>429</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>431</v>
+      </c>
+      <c r="B41" t="s">
+        <v>432</v>
+      </c>
+      <c r="C41" t="s">
+        <v>433</v>
+      </c>
+      <c r="D41" t="s">
+        <v>434</v>
+      </c>
+      <c r="E41" t="s">
+        <v>261</v>
+      </c>
+      <c r="F41" t="s">
+        <v>261</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>436</v>
+      </c>
+      <c r="B42" t="s">
+        <v>437</v>
+      </c>
+      <c r="C42" t="s">
+        <v>438</v>
+      </c>
+      <c r="D42" t="s">
+        <v>244</v>
+      </c>
+      <c r="E42" t="s">
+        <v>261</v>
+      </c>
+      <c r="F42" t="s">
+        <v>439</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>441</v>
+      </c>
+      <c r="B43" t="s">
+        <v>442</v>
+      </c>
+      <c r="C43" t="s">
+        <v>443</v>
+      </c>
+      <c r="D43" t="s">
+        <v>237</v>
+      </c>
+      <c r="E43" t="s">
+        <v>444</v>
+      </c>
+      <c r="F43" t="s">
+        <v>261</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>446</v>
+      </c>
+      <c r="B44" t="s">
+        <v>447</v>
+      </c>
+      <c r="C44" t="s">
+        <v>335</v>
+      </c>
+      <c r="D44" t="s">
+        <v>237</v>
+      </c>
+      <c r="E44" t="s">
+        <v>448</v>
+      </c>
+      <c r="F44" t="s">
+        <v>449</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>451</v>
+      </c>
+      <c r="B45" t="s">
+        <v>452</v>
+      </c>
+      <c r="C45" t="s">
+        <v>229</v>
+      </c>
+      <c r="D45" t="s">
+        <v>237</v>
+      </c>
+      <c r="E45" t="s">
+        <v>453</v>
+      </c>
+      <c r="F45" t="s">
+        <v>454</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" t="s">
+        <v>456</v>
+      </c>
+      <c r="C46" t="s">
+        <v>457</v>
+      </c>
+      <c r="D46" t="s">
+        <v>244</v>
+      </c>
+      <c r="E46" t="s">
+        <v>458</v>
+      </c>
+      <c r="F46" t="s">
+        <v>459</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>461</v>
+      </c>
+      <c r="B47" t="s">
+        <v>462</v>
+      </c>
+      <c r="C47" t="s">
+        <v>463</v>
+      </c>
+      <c r="D47" t="s">
+        <v>277</v>
+      </c>
+      <c r="E47" t="s">
+        <v>464</v>
+      </c>
+      <c r="F47" t="s">
+        <v>320</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>466</v>
+      </c>
+      <c r="B48" t="s">
+        <v>467</v>
+      </c>
+      <c r="C48" t="s">
+        <v>468</v>
+      </c>
+      <c r="D48" t="s">
+        <v>237</v>
+      </c>
+      <c r="E48" t="s">
+        <v>469</v>
+      </c>
+      <c r="F48" t="s">
+        <v>470</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>472</v>
+      </c>
+      <c r="B49" t="s">
+        <v>356</v>
+      </c>
+      <c r="C49" t="s">
+        <v>473</v>
+      </c>
+      <c r="D49" t="s">
+        <v>237</v>
+      </c>
+      <c r="E49" t="s">
+        <v>358</v>
+      </c>
+      <c r="F49" t="s">
+        <v>359</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>475</v>
+      </c>
+      <c r="B50" t="s">
+        <v>476</v>
+      </c>
+      <c r="C50" t="s">
+        <v>229</v>
+      </c>
+      <c r="D50" t="s">
+        <v>237</v>
+      </c>
+      <c r="E50" t="s">
+        <v>477</v>
+      </c>
+      <c r="F50" t="s">
+        <v>478</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>475</v>
+      </c>
+      <c r="B51" t="s">
+        <v>480</v>
+      </c>
+      <c r="C51" t="s">
+        <v>259</v>
+      </c>
+      <c r="D51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E51" t="s">
+        <v>481</v>
+      </c>
+      <c r="F51" t="s">
+        <v>325</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>483</v>
+      </c>
+      <c r="B52" t="s">
+        <v>484</v>
+      </c>
+      <c r="C52" t="s">
+        <v>485</v>
+      </c>
+      <c r="D52" t="s">
+        <v>237</v>
+      </c>
+      <c r="E52" t="s">
+        <v>486</v>
+      </c>
+      <c r="F52" t="s">
+        <v>487</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>489</v>
+      </c>
+      <c r="B53" t="s">
+        <v>490</v>
+      </c>
+      <c r="C53" t="s">
+        <v>229</v>
+      </c>
+      <c r="D53" t="s">
+        <v>434</v>
+      </c>
+      <c r="E53" t="s">
+        <v>347</v>
+      </c>
+      <c r="F53" t="s">
+        <v>491</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>493</v>
+      </c>
+      <c r="B54" t="s">
+        <v>269</v>
+      </c>
+      <c r="C54" t="s">
+        <v>270</v>
+      </c>
+      <c r="D54" t="s">
+        <v>237</v>
+      </c>
+      <c r="E54" t="s">
+        <v>494</v>
+      </c>
+      <c r="F54" t="s">
+        <v>272</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>496</v>
+      </c>
+      <c r="B55" t="s">
+        <v>497</v>
+      </c>
+      <c r="C55" t="s">
+        <v>498</v>
+      </c>
+      <c r="D55" t="s">
+        <v>237</v>
+      </c>
+      <c r="E55" t="s">
+        <v>499</v>
+      </c>
+      <c r="F55" t="s">
+        <v>500</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>502</v>
+      </c>
+      <c r="B56" t="s">
+        <v>503</v>
+      </c>
+      <c r="C56" t="s">
+        <v>335</v>
+      </c>
+      <c r="D56" t="s">
+        <v>237</v>
+      </c>
+      <c r="E56" t="s">
+        <v>504</v>
+      </c>
+      <c r="F56" t="s">
+        <v>505</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>507</v>
+      </c>
+      <c r="B57" t="s">
+        <v>503</v>
+      </c>
+      <c r="C57" t="s">
+        <v>335</v>
+      </c>
+      <c r="D57" t="s">
+        <v>237</v>
+      </c>
+      <c r="E57" t="s">
+        <v>504</v>
+      </c>
+      <c r="F57" t="s">
+        <v>505</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>509</v>
+      </c>
+      <c r="B58" t="s">
+        <v>503</v>
+      </c>
+      <c r="C58" t="s">
+        <v>335</v>
+      </c>
+      <c r="D58" t="s">
+        <v>237</v>
+      </c>
+      <c r="E58" t="s">
+        <v>504</v>
+      </c>
+      <c r="F58" t="s">
+        <v>505</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>511</v>
+      </c>
+      <c r="B59" t="s">
+        <v>512</v>
+      </c>
+      <c r="C59" t="s">
+        <v>443</v>
+      </c>
+      <c r="D59" t="s">
+        <v>237</v>
+      </c>
+      <c r="E59" t="s">
+        <v>309</v>
+      </c>
+      <c r="F59" t="s">
+        <v>261</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>514</v>
+      </c>
+      <c r="B60" t="s">
+        <v>515</v>
+      </c>
+      <c r="C60" t="s">
+        <v>229</v>
+      </c>
+      <c r="D60" t="s">
+        <v>237</v>
+      </c>
+      <c r="E60" t="s">
+        <v>516</v>
+      </c>
+      <c r="F60" t="s">
+        <v>517</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>519</v>
+      </c>
+      <c r="B61" t="s">
+        <v>520</v>
+      </c>
+      <c r="C61" t="s">
+        <v>521</v>
+      </c>
+      <c r="D61" t="s">
+        <v>237</v>
+      </c>
+      <c r="E61" t="s">
+        <v>522</v>
+      </c>
+      <c r="F61" t="s">
+        <v>523</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>525</v>
+      </c>
+      <c r="B62" t="s">
+        <v>526</v>
+      </c>
+      <c r="C62" t="s">
+        <v>229</v>
+      </c>
+      <c r="D62" t="s">
+        <v>237</v>
+      </c>
+      <c r="E62" t="s">
+        <v>527</v>
+      </c>
+      <c r="F62" t="s">
+        <v>528</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>530</v>
+      </c>
+      <c r="B63" t="s">
+        <v>531</v>
+      </c>
+      <c r="C63" t="s">
+        <v>416</v>
+      </c>
+      <c r="D63" t="s">
+        <v>237</v>
+      </c>
+      <c r="E63" t="s">
+        <v>532</v>
+      </c>
+      <c r="F63" t="s">
+        <v>533</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>535</v>
+      </c>
+      <c r="B64" t="s">
+        <v>536</v>
+      </c>
+      <c r="C64" t="s">
+        <v>537</v>
+      </c>
+      <c r="D64" t="s">
+        <v>237</v>
+      </c>
+      <c r="E64" t="s">
+        <v>538</v>
+      </c>
+      <c r="F64" t="s">
+        <v>539</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>541</v>
+      </c>
+      <c r="B65" t="s">
+        <v>542</v>
+      </c>
+      <c r="C65" t="s">
+        <v>443</v>
+      </c>
+      <c r="D65" t="s">
+        <v>237</v>
+      </c>
+      <c r="E65" t="s">
+        <v>336</v>
+      </c>
+      <c r="F65" t="s">
+        <v>543</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>545</v>
+      </c>
+      <c r="B66" t="s">
+        <v>546</v>
+      </c>
+      <c r="C66" t="s">
+        <v>283</v>
+      </c>
+      <c r="D66" t="s">
+        <v>237</v>
+      </c>
+      <c r="E66" t="s">
+        <v>309</v>
+      </c>
+      <c r="F66" t="s">
+        <v>261</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>548</v>
+      </c>
+      <c r="B67" t="s">
+        <v>549</v>
+      </c>
+      <c r="C67" t="s">
+        <v>550</v>
+      </c>
+      <c r="D67" t="s">
+        <v>237</v>
+      </c>
+      <c r="E67" t="s">
+        <v>261</v>
+      </c>
+      <c r="F67" t="s">
+        <v>429</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>552</v>
+      </c>
+      <c r="B68" t="s">
+        <v>553</v>
+      </c>
+      <c r="C68" t="s">
+        <v>554</v>
+      </c>
+      <c r="D68" t="s">
+        <v>244</v>
+      </c>
+      <c r="E68" t="s">
+        <v>555</v>
+      </c>
+      <c r="F68" t="s">
+        <v>556</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>558</v>
+      </c>
+      <c r="B69" t="s">
+        <v>559</v>
+      </c>
+      <c r="C69" t="s">
+        <v>416</v>
+      </c>
+      <c r="D69" t="s">
+        <v>237</v>
+      </c>
+      <c r="E69" t="s">
+        <v>560</v>
+      </c>
+      <c r="F69" t="s">
+        <v>561</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>563</v>
+      </c>
+      <c r="B70" t="s">
+        <v>564</v>
+      </c>
+      <c r="C70" t="s">
+        <v>565</v>
+      </c>
+      <c r="D70" t="s">
+        <v>237</v>
+      </c>
+      <c r="E70" t="s">
+        <v>566</v>
+      </c>
+      <c r="F70" t="s">
+        <v>567</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>569</v>
+      </c>
+      <c r="B71" t="s">
+        <v>570</v>
+      </c>
+      <c r="C71" t="s">
+        <v>443</v>
+      </c>
+      <c r="D71" t="s">
+        <v>237</v>
+      </c>
+      <c r="E71" t="s">
+        <v>238</v>
+      </c>
+      <c r="F71" t="s">
+        <v>571</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>573</v>
+      </c>
+      <c r="B72" t="s">
+        <v>574</v>
+      </c>
+      <c r="C72" t="s">
+        <v>575</v>
+      </c>
+      <c r="D72" t="s">
+        <v>237</v>
+      </c>
+      <c r="E72" t="s">
+        <v>576</v>
+      </c>
+      <c r="F72" t="s">
+        <v>325</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>578</v>
+      </c>
+      <c r="B73" t="s">
+        <v>579</v>
+      </c>
+      <c r="C73" t="s">
+        <v>580</v>
+      </c>
+      <c r="D73" t="s">
+        <v>237</v>
+      </c>
+      <c r="E73" t="s">
+        <v>581</v>
+      </c>
+      <c r="F73" t="s">
+        <v>582</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>584</v>
+      </c>
+      <c r="B74" t="s">
+        <v>579</v>
+      </c>
+      <c r="C74" t="s">
+        <v>580</v>
+      </c>
+      <c r="D74" t="s">
+        <v>237</v>
+      </c>
+      <c r="E74" t="s">
+        <v>581</v>
+      </c>
+      <c r="F74" t="s">
+        <v>585</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>587</v>
+      </c>
+      <c r="B75" t="s">
+        <v>579</v>
+      </c>
+      <c r="C75" t="s">
+        <v>580</v>
+      </c>
+      <c r="D75" t="s">
+        <v>237</v>
+      </c>
+      <c r="E75" t="s">
+        <v>581</v>
+      </c>
+      <c r="F75" t="s">
+        <v>582</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>589</v>
+      </c>
+      <c r="B76" t="s">
+        <v>590</v>
+      </c>
+      <c r="C76" t="s">
+        <v>229</v>
+      </c>
+      <c r="D76" t="s">
+        <v>237</v>
+      </c>
+      <c r="E76" t="s">
+        <v>591</v>
+      </c>
+      <c r="F76" t="s">
+        <v>592</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>594</v>
+      </c>
+      <c r="B77" t="s">
+        <v>595</v>
+      </c>
+      <c r="C77" t="s">
+        <v>596</v>
+      </c>
+      <c r="D77" t="s">
+        <v>237</v>
+      </c>
+      <c r="E77" t="s">
+        <v>278</v>
+      </c>
+      <c r="F77" t="s">
+        <v>597</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>599</v>
+      </c>
+      <c r="B78" t="s">
+        <v>553</v>
+      </c>
+      <c r="C78" t="s">
+        <v>554</v>
+      </c>
+      <c r="D78" t="s">
+        <v>237</v>
+      </c>
+      <c r="E78" t="s">
+        <v>600</v>
+      </c>
+      <c r="F78" t="s">
+        <v>556</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>602</v>
+      </c>
+      <c r="B79" t="s">
+        <v>603</v>
+      </c>
+      <c r="C79" t="s">
+        <v>283</v>
+      </c>
+      <c r="D79" t="s">
+        <v>237</v>
+      </c>
+      <c r="E79" t="s">
+        <v>604</v>
+      </c>
+      <c r="F79" t="s">
+        <v>605</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>607</v>
+      </c>
+      <c r="B80" t="s">
+        <v>608</v>
+      </c>
+      <c r="C80" t="s">
+        <v>609</v>
+      </c>
+      <c r="D80" t="s">
+        <v>237</v>
+      </c>
+      <c r="E80" t="s">
+        <v>610</v>
+      </c>
+      <c r="F80" t="s">
+        <v>611</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>613</v>
+      </c>
+      <c r="B81" t="s">
+        <v>252</v>
+      </c>
+      <c r="C81" t="s">
+        <v>229</v>
+      </c>
+      <c r="D81" t="s">
+        <v>244</v>
+      </c>
+      <c r="E81" t="s">
+        <v>614</v>
+      </c>
+      <c r="F81" t="s">
+        <v>255</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>616</v>
+      </c>
+      <c r="B82" t="s">
+        <v>520</v>
+      </c>
+      <c r="C82" t="s">
+        <v>617</v>
+      </c>
+      <c r="D82" t="s">
+        <v>237</v>
+      </c>
+      <c r="E82" t="s">
+        <v>618</v>
+      </c>
+      <c r="F82" t="s">
+        <v>619</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>621</v>
+      </c>
+      <c r="B83" t="s">
+        <v>622</v>
+      </c>
+      <c r="C83" t="s">
+        <v>623</v>
+      </c>
+      <c r="D83" t="s">
+        <v>237</v>
+      </c>
+      <c r="E83" t="s">
+        <v>624</v>
+      </c>
+      <c r="F83" t="s">
+        <v>625</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>627</v>
+      </c>
+      <c r="B84" t="s">
+        <v>628</v>
+      </c>
+      <c r="C84" t="s">
+        <v>629</v>
+      </c>
+      <c r="D84" t="s">
+        <v>237</v>
+      </c>
+      <c r="E84" t="s">
+        <v>630</v>
+      </c>
+      <c r="F84" t="s">
+        <v>261</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>632</v>
+      </c>
+      <c r="B85" t="s">
+        <v>484</v>
+      </c>
+      <c r="C85" t="s">
+        <v>485</v>
+      </c>
+      <c r="D85" t="s">
+        <v>237</v>
+      </c>
+      <c r="E85" t="s">
+        <v>633</v>
+      </c>
+      <c r="F85" t="s">
+        <v>487</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>635</v>
+      </c>
+      <c r="B86" t="s">
+        <v>484</v>
+      </c>
+      <c r="C86" t="s">
+        <v>485</v>
+      </c>
+      <c r="D86" t="s">
+        <v>237</v>
+      </c>
+      <c r="E86" t="s">
+        <v>636</v>
+      </c>
+      <c r="F86" t="s">
+        <v>637</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>639</v>
+      </c>
+      <c r="B87" t="s">
+        <v>640</v>
+      </c>
+      <c r="C87" t="s">
+        <v>641</v>
+      </c>
+      <c r="D87" t="s">
+        <v>237</v>
+      </c>
+      <c r="E87" t="s">
+        <v>642</v>
+      </c>
+      <c r="F87" t="s">
+        <v>325</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>644</v>
+      </c>
+      <c r="B88" t="s">
+        <v>645</v>
+      </c>
+      <c r="C88" t="s">
+        <v>646</v>
+      </c>
+      <c r="D88" t="s">
+        <v>237</v>
+      </c>
+      <c r="E88" t="s">
+        <v>647</v>
+      </c>
+      <c r="F88" t="s">
+        <v>261</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>649</v>
+      </c>
+      <c r="B89" t="s">
+        <v>622</v>
+      </c>
+      <c r="C89" t="s">
+        <v>283</v>
+      </c>
+      <c r="D89" t="s">
+        <v>237</v>
+      </c>
+      <c r="E89" t="s">
+        <v>650</v>
+      </c>
+      <c r="F89" t="s">
+        <v>625</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>652</v>
+      </c>
+      <c r="B90" t="s">
+        <v>653</v>
+      </c>
+      <c r="C90" t="s">
+        <v>229</v>
+      </c>
+      <c r="D90" t="s">
+        <v>237</v>
+      </c>
+      <c r="E90" t="s">
+        <v>654</v>
+      </c>
+      <c r="F90" t="s">
+        <v>655</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>657</v>
+      </c>
+      <c r="B91" t="s">
+        <v>658</v>
+      </c>
+      <c r="C91" t="s">
+        <v>659</v>
+      </c>
+      <c r="D91" t="s">
+        <v>237</v>
+      </c>
+      <c r="E91" t="s">
+        <v>499</v>
+      </c>
+      <c r="F91" t="s">
+        <v>660</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>662</v>
+      </c>
+      <c r="B92" t="s">
+        <v>663</v>
+      </c>
+      <c r="C92" t="s">
+        <v>229</v>
+      </c>
+      <c r="D92" t="s">
+        <v>237</v>
+      </c>
+      <c r="E92" t="s">
+        <v>664</v>
+      </c>
+      <c r="F92" t="s">
+        <v>665</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>667</v>
+      </c>
+      <c r="B93" t="s">
+        <v>668</v>
+      </c>
+      <c r="C93" t="s">
+        <v>380</v>
+      </c>
+      <c r="D93" t="s">
+        <v>237</v>
+      </c>
+      <c r="E93" t="s">
+        <v>669</v>
+      </c>
+      <c r="F93" t="s">
+        <v>670</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>672</v>
+      </c>
+      <c r="B94" t="s">
+        <v>673</v>
+      </c>
+      <c r="C94" t="s">
+        <v>443</v>
+      </c>
+      <c r="D94" t="s">
+        <v>237</v>
+      </c>
+      <c r="E94" t="s">
+        <v>674</v>
+      </c>
+      <c r="F94" t="s">
+        <v>325</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>676</v>
+      </c>
+      <c r="B95" t="s">
+        <v>677</v>
+      </c>
+      <c r="C95" t="s">
+        <v>678</v>
+      </c>
+      <c r="D95" t="s">
+        <v>244</v>
+      </c>
+      <c r="E95" t="s">
+        <v>679</v>
+      </c>
+      <c r="F95" t="s">
+        <v>660</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>681</v>
+      </c>
+      <c r="B96" t="s">
+        <v>682</v>
+      </c>
+      <c r="C96" t="s">
+        <v>283</v>
+      </c>
+      <c r="D96" t="s">
+        <v>237</v>
+      </c>
+      <c r="E96" t="s">
+        <v>683</v>
+      </c>
+      <c r="F96" t="s">
+        <v>684</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>227</v>
+      </c>
+      <c r="B97" t="s">
+        <v>228</v>
+      </c>
+      <c r="C97" t="s">
+        <v>229</v>
+      </c>
+      <c r="D97" t="s">
+        <v>237</v>
+      </c>
+      <c r="E97" t="s">
+        <v>238</v>
+      </c>
+      <c r="F97" t="s">
+        <v>533</v>
+      </c>
+      <c r="G97" t="s">
+        <v>686</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>688</v>
+      </c>
+      <c r="B98" t="s">
+        <v>520</v>
+      </c>
+      <c r="C98" t="s">
+        <v>689</v>
+      </c>
+      <c r="D98" t="s">
+        <v>237</v>
+      </c>
+      <c r="E98" t="s">
+        <v>690</v>
+      </c>
+      <c r="F98" t="s">
+        <v>691</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>693</v>
+      </c>
+      <c r="B99" t="s">
+        <v>694</v>
+      </c>
+      <c r="C99" t="s">
+        <v>695</v>
+      </c>
+      <c r="D99" t="s">
+        <v>237</v>
+      </c>
+      <c r="E99" t="s">
+        <v>696</v>
+      </c>
+      <c r="F99" t="s">
+        <v>697</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>699</v>
+      </c>
+      <c r="B100" t="s">
+        <v>700</v>
+      </c>
+      <c r="C100" t="s">
+        <v>701</v>
+      </c>
+      <c r="D100" t="s">
+        <v>237</v>
+      </c>
+      <c r="E100" t="s">
+        <v>702</v>
+      </c>
+      <c r="F100" t="s">
+        <v>703</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>705</v>
+      </c>
+      <c r="B101" t="s">
+        <v>706</v>
+      </c>
+      <c r="C101" t="s">
+        <v>443</v>
+      </c>
+      <c r="D101" t="s">
+        <v>237</v>
+      </c>
+      <c r="E101" t="s">
+        <v>707</v>
+      </c>
+      <c r="F101" t="s">
+        <v>708</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>710</v>
+      </c>
+      <c r="B102" t="s">
+        <v>711</v>
+      </c>
+      <c r="C102" t="s">
+        <v>712</v>
+      </c>
+      <c r="D102" t="s">
+        <v>237</v>
+      </c>
+      <c r="E102" t="s">
+        <v>713</v>
+      </c>
+      <c r="F102" t="s">
+        <v>582</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>715</v>
+      </c>
+      <c r="B103" t="s">
+        <v>716</v>
+      </c>
+      <c r="C103" t="s">
+        <v>380</v>
+      </c>
+      <c r="D103" t="s">
+        <v>277</v>
+      </c>
+      <c r="E103" t="s">
+        <v>717</v>
+      </c>
+      <c r="F103" t="s">
+        <v>718</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>715</v>
+      </c>
+      <c r="B104" t="s">
+        <v>716</v>
+      </c>
+      <c r="C104" t="s">
+        <v>720</v>
+      </c>
+      <c r="D104" t="s">
+        <v>277</v>
+      </c>
+      <c r="E104" t="s">
+        <v>717</v>
+      </c>
+      <c r="F104" t="s">
+        <v>718</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>722</v>
+      </c>
+      <c r="B105" t="s">
+        <v>723</v>
+      </c>
+      <c r="C105" t="s">
+        <v>283</v>
+      </c>
+      <c r="D105" t="s">
+        <v>244</v>
+      </c>
+      <c r="E105" t="s">
+        <v>724</v>
+      </c>
+      <c r="F105" t="s">
+        <v>660</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>726</v>
+      </c>
+      <c r="B106" t="s">
+        <v>727</v>
+      </c>
+      <c r="C106" t="s">
+        <v>728</v>
+      </c>
+      <c r="D106" t="s">
+        <v>237</v>
+      </c>
+      <c r="E106" t="s">
+        <v>729</v>
+      </c>
+      <c r="F106" t="s">
+        <v>449</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>731</v>
+      </c>
+      <c r="B107" t="s">
+        <v>711</v>
+      </c>
+      <c r="C107" t="s">
+        <v>732</v>
+      </c>
+      <c r="D107" t="s">
+        <v>237</v>
+      </c>
+      <c r="E107" t="s">
+        <v>733</v>
+      </c>
+      <c r="F107" t="s">
+        <v>449</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-07.xlsx
+++ b/docs/xlsx/jobs-2026-10-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="892">
   <si>
     <t>Title</t>
   </si>
@@ -697,6 +697,27 @@
     <t>https://www.conservationjobboard.com/job-listing-wyoming-conservation-manager-jackson-lander-ft-washakie-or-cody-wyoming/5790286193</t>
   </si>
   <si>
+    <t>Administration and Operations Manager</t>
+  </si>
+  <si>
+    <t>Capitol Region Watershed District</t>
+  </si>
+  <si>
+    <t>Saint Paul, Minnesota, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>80,000 - 100,000</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/administration-and-operations-manager/</t>
+  </si>
+  <si>
     <t>Southeastern States Conservation Manager</t>
   </si>
   <si>
@@ -706,9 +727,6 @@
     <t>Remote</t>
   </si>
   <si>
-    <t>Full-Time</t>
-  </si>
-  <si>
     <t>60,000 - 80,000</t>
   </si>
   <si>
@@ -949,6 +967,24 @@
     <t>https://www.idealist.org/en/job/41d1f849526a41c3926d94a6aed19c25-client-engagement-administrator-npag-beaverton</t>
   </si>
   <si>
+    <t>Climate Resilience Organizer</t>
+  </si>
+  <si>
+    <t>AZ AANHPI</t>
+  </si>
+  <si>
+    <t>Tempe, Arizona</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45d6fe4d95604a6ab0561ce0e39b2a62-climate-resilience-organizer-az-aanhpi-tempe</t>
+  </si>
+  <si>
     <t>Clinical Monitor</t>
   </si>
   <si>
@@ -1033,6 +1069,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/864e8bfb8e814328aecb833c159465aa-community-economic-development-manager-northwest-side-community-development-corporation-chicago</t>
   </si>
   <si>
+    <t>Community Engagement Director</t>
+  </si>
+  <si>
+    <t>Ventura Land Trust</t>
+  </si>
+  <si>
+    <t>Ventura, California</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aad67def22e547f2847d55d0c09faa9a-community-engagement-director-ventura-land-trust-ventura</t>
+  </si>
+  <si>
     <t>Community Service Coordinator and Custodian of Building &amp; Grounds</t>
   </si>
   <si>
@@ -1081,6 +1135,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/2fc76cdc59f74d23ab25eb66288480db-conservation-project-manager-mount-desert-island-maine-coast-heritage-trust-mount-desert</t>
   </si>
   <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>AidKit</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/cdc79e20289b479b96238c98d33feb49-controller-aidkit-boulder</t>
+  </si>
+  <si>
+    <t>Coordinator, EDF Action</t>
+  </si>
+  <si>
+    <t>Environmental Defense Fund</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3dedf9c9a6cd4368ae92d886d287c5ab-coordinator-edf-action-environmental-defense-fund-washington</t>
+  </si>
+  <si>
     <t>Crisis Response Counselor</t>
   </si>
   <si>
@@ -1132,6 +1213,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/444598fc071c40a8932d3cb75d4f2219-customer-relations-manager-american-speech-language-hearing-association-rockville</t>
   </si>
   <si>
+    <t>Data and Systems Coordinator</t>
+  </si>
+  <si>
+    <t>Read Alliance</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a42c0d17a414fb29b6eb98f27e9da2b-data-and-systems-coordinator-read-alliance-new-york</t>
+  </si>
+  <si>
     <t>Deputy Chief Program Officer</t>
   </si>
   <si>
@@ -1162,9 +1261,6 @@
     <t>USD 80000.00 - 100000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/0f85b8c53d044909b680166df3e17557-development-director-posse-bay-area-the-posse-foundation-inc-san-francisco</t>
   </si>
   <si>
@@ -1174,6 +1270,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/4a7989fc3a3e432bb053bd921fffd772-development-director-posse-los-angeles-the-posse-foundation-inc-los-angeles</t>
   </si>
   <si>
+    <t>Development Review Coordinator</t>
+  </si>
+  <si>
+    <t>Chestnut Hill Conservancy</t>
+  </si>
+  <si>
+    <t>USD 60.00 - 60.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0cf75bfab54f48298fa1c8fd485ddfa2-development-review-coordinator-chestnut-hill-conservancy-philadelphia</t>
+  </si>
+  <si>
+    <t>Development Writer</t>
+  </si>
+  <si>
+    <t>Human Rights Watch</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 88000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/83d95bece5fc4cc7a9c6e4343b3cbd28-development-writer-human-rights-watch-new-york</t>
+  </si>
+  <si>
     <t>Digital Coordinator II</t>
   </si>
   <si>
@@ -1225,6 +1351,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/763064725fbc492ab678455ac4bba4a3-director-of-development-goddard-house-in-brookline-assisted-living-brookline</t>
   </si>
   <si>
+    <t>Asian American Drug Abuse Program, Inc. (AADAP)</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health, Substance Abuse Addiction, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6f236047d694bacb4a0eeb0d6882454-director-of-development-asian-american-drug-abuse-program-inc-aadap-los-angeles</t>
+  </si>
+  <si>
     <t>Director of Education</t>
   </si>
   <si>
@@ -1243,6 +1381,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/ce3c2c39a5e546d1aa128b6ab320fcaa-director-of-education-valley-beit-midrash-scottsdale</t>
   </si>
   <si>
+    <t>Director of Engagement</t>
+  </si>
+  <si>
+    <t>Nourish California</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Hunger Food Security, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a5232c86170845d38f60ae1b483e3199-director-of-engagement-nourish-california-oakland</t>
+  </si>
+  <si>
     <t>Director of Litigation and Special Projects</t>
   </si>
   <si>
@@ -1264,9 +1420,6 @@
     <t>Rise Economy</t>
   </si>
   <si>
-    <t>Remote (California)</t>
-  </si>
-  <si>
     <t>Community Development, Economic Development, Microfinance</t>
   </si>
   <si>
@@ -1333,9 +1486,6 @@
     <t>Buenos Aires, Buenos Aires, AR</t>
   </si>
   <si>
-    <t>Human Rights Civil Liberties</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/491a60fd859b433b88dbe8b338b46531-en-amnistia-internacional-buscamos-captadores-de-fondos-en-via-publica-para-caba-amnistia-internacional-argentina-buenos-aires</t>
   </si>
   <si>
@@ -1345,9 +1495,6 @@
     <t>Meridian International Center</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 19.00 - 20.00/hour</t>
   </si>
   <si>
@@ -1384,6 +1531,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/f07c15f8ac3e4b75a44021cf6635ea91-events-manager-tech-coalition-reston</t>
   </si>
   <si>
+    <t>Executive Assistant &amp; Constituent Relations Associate</t>
+  </si>
+  <si>
+    <t>The Mizel Institute</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d83f99d34964012a13e3e8d5b02b5b4-executive-assistant-constituent-relations-associate-the-mizel-institute-denver</t>
+  </si>
+  <si>
     <t>Placer Nature Center</t>
   </si>
   <si>
@@ -1399,6 +1564,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/8cbf8af7cf0b4e529aa989e245279104-executive-director-placer-nature-center-auburn</t>
   </si>
   <si>
+    <t>CALICO Center</t>
+  </si>
+  <si>
+    <t>San Leandro, California</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6859730c097a4bdca7258260982fea07-executive-director-calico-center-san-leandro</t>
+  </si>
+  <si>
+    <t>The Alliance Chaffee County</t>
+  </si>
+  <si>
+    <t>Salida, Colorado</t>
+  </si>
+  <si>
+    <t>Mental Health, Victim Support, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f7f55d5e3d440dd93d7604c93ffc4b8-executive-director-the-alliance-chaffee-county-salida</t>
+  </si>
+  <si>
     <t>Facilitador/a Educativo/a en CDMX/ Edo. Mex( Virtual)</t>
   </si>
   <si>
@@ -1441,6 +1633,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/4bf72ef5e05440fa8fda611fcce91942-foster-care-specialist-youth-villages-jackson</t>
   </si>
   <si>
+    <t>Fundraising &amp; Grants Member Advisors</t>
+  </si>
+  <si>
+    <t>Fractured Atlas</t>
+  </si>
+  <si>
+    <t>USD 68016.00 - 68016.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Financial Literacy Personal Finance, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/900de03b0f1a4cc6bd11d31307daa25f-fundraising-grants-member-advisors-fractured-atlas-new-york</t>
+  </si>
+  <si>
     <t>Grants Manager</t>
   </si>
   <si>
@@ -1483,6 +1690,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/663e4f131f964190866fdd291e5c9d26-housing-case-manager-safe-alternatives-to-violent-environments-fremont</t>
   </si>
   <si>
+    <t>HR Manager</t>
+  </si>
+  <si>
+    <t>Southwest Youth and Family Services</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d48307169f8a412cb9d7302116c67db2-hr-manager-southwest-youth-and-family-services-seattle</t>
+  </si>
+  <si>
     <t>International Programs Manager (Bilingual in English &amp; Spanish)</t>
   </si>
   <si>
@@ -1504,6 +1726,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/b1664df9bce44f9fa646046897fc48ec-investigative-advocate-representative-payee-team-disability-rights-md-baltimore</t>
   </si>
   <si>
+    <t>Jeremiah Program- Boston: Family Services Director</t>
+  </si>
+  <si>
+    <t>Jeremiah Program_Minneapolis</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 92000.00 - 102000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Conflict Resolution, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b101476b091481baeec1343d40358b8-jeremiah-program-boston-family-services-director-jeremiah-programminneapolis-boston</t>
+  </si>
+  <si>
     <t>Job Placement Manager</t>
   </si>
   <si>
@@ -1522,6 +1762,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/d84654e404e345409156c1973fa7a6a6-job-placement-manager-emmas-torch-kings-county</t>
   </si>
   <si>
+    <t>Leadership in Financial Education (LIFE) Program Coordinator</t>
+  </si>
+  <si>
+    <t>Leadership in Financial Education</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a5d350734846457099c761df89b25609-leadership-in-financial-education-life-program-coordinator-leadership-in-financial-education-new-york</t>
+  </si>
+  <si>
     <t>Manager of Learning and Development</t>
   </si>
   <si>
@@ -1573,6 +1825,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/8c174920e3f04542827cd277828edbfc-managing-director-collaborative-capital-gitlab-foundation-san-francisco</t>
   </si>
   <si>
+    <t>Marketing and Donor Engagement Manager</t>
+  </si>
+  <si>
+    <t>University of New Mexico</t>
+  </si>
+  <si>
+    <t>Albuquerque, New Mexico</t>
+  </si>
+  <si>
+    <t>USD 4924.00 - 7046.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/427e60fa58a24e5d97eccf622073bedc-marketing-and-donor-engagement-manager-university-of-new-mexico-albuquerque</t>
+  </si>
+  <si>
     <t>Medical Director in Belize - Live Abroad</t>
   </si>
   <si>
@@ -1609,15 +1876,9 @@
     <t>Mid-Level Giving Officer</t>
   </si>
   <si>
-    <t>Environmental Defense Fund</t>
-  </si>
-  <si>
     <t>USD 88000.00 - 94000.00/year</t>
   </si>
   <si>
-    <t>Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/a048c301eac24f86a2c7ddd40e4caf05-mid-level-giving-officer-environmental-defense-fund-new-york</t>
   </si>
   <si>
@@ -1660,6 +1921,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/471d5ba397bf436dbec55e59aa884b1a-operations-manager-tsne-new-york</t>
   </si>
   <si>
+    <t>Friends of the Children - SF Bay Area</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/74d56a9d118b4403bb7de311bf82bb00-operations-manager-friends-of-the-children-sf-bay-area-san-francisco</t>
+  </si>
+  <si>
     <t>Outreach, Education &amp; Prevention Specialist</t>
   </si>
   <si>
@@ -1672,6 +1942,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/b63b34b0454a4a68ace21ecd282df73d-outreach-education-prevention-specialist-independence-house-inc-barnstable</t>
   </si>
   <si>
+    <t>Part Time Program Coordinator, Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>Read to a Child</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5cb48c62535c43a58a2963becaba0fb2-part-time-program-coordinator-los-angeles-ca-read-to-a-child-los-angeles</t>
+  </si>
+  <si>
     <t>Part-Time Bookkeeper – Nonprofit Fund Accounting</t>
   </si>
   <si>
@@ -1723,6 +2005,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/d3a65893c9684d70bb44b4a7828e23c5-policy-coordinator-lpsc-miso-alliance-for-affordable-energy-new-orleans</t>
   </si>
   <si>
+    <t>Policy Director</t>
+  </si>
+  <si>
+    <t>Municipal Research and Services Center of Washington</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6e72040441a48ada7ea5672e12ec43a-policy-director-municipal-research-and-services-center-of-washington-tacoma</t>
+  </si>
+  <si>
     <t>Policy Project Manager, Retirement</t>
   </si>
   <si>
@@ -1762,9 +2062,6 @@
     <t>USD 35000.00 - 60000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/2e6c3e7864c04a98a2116ee3f17cb0a2-primary-english-and-social-studies-teacher-proea-pro-educacion-y-ambiente-rincon</t>
   </si>
   <si>
@@ -1789,9 +2086,6 @@
     <t>FundMiner</t>
   </si>
   <si>
-    <t>USD 65000.00 - 80000.00/year</t>
-  </si>
-  <si>
     <t>Entrepreneurship, Science Technology</t>
   </si>
   <si>
@@ -1837,6 +2131,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/f7f41614746641878495c15ff48fece7-program-manager-partnerships-pencil-new-york</t>
   </si>
   <si>
+    <t>Program Specialist</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8a5e10d93ad4e44bcfe1fb9cd5bd9d0-program-specialist-southwest-youth-and-family-services-seattle</t>
+  </si>
+  <si>
     <t>Program Specialist-Community Specialist</t>
   </si>
   <si>
@@ -1855,6 +2161,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/60acf6b1efa24ba78c24440567642d08-program-specialist-community-specialist-vermont-foodbank-barre</t>
   </si>
   <si>
+    <t>Project Rise Program Coordinator</t>
+  </si>
+  <si>
+    <t>Operation Shoestring</t>
+  </si>
+  <si>
+    <t>Jackson, Mississippi</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff6e60ea75cb4031adb144fad27acdda-project-rise-program-coordinator-operation-shoestring-jackson</t>
+  </si>
+  <si>
+    <t>Property Management Administrative Associate</t>
+  </si>
+  <si>
+    <t>Fifth Avenue Committee, Inc.</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 27.50/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/131f5e8a5d4e4af89358bce71af8c542-property-management-administrative-associate-fifth-avenue-committee-inc-brooklyn</t>
+  </si>
+  <si>
     <t>Provincial Sustainability Assistant</t>
   </si>
   <si>
@@ -1864,6 +2206,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/205e6c6e454f45509d38613df07b520d-provincial-sustainability-assistant-the-felician-sisters-of-north-america-beaver-falls</t>
   </si>
   <si>
+    <t>Psicóloga Institucional Hogar ADOLESCENTES ( es requisito viva en zona - EXCLUYENTE)</t>
+  </si>
+  <si>
+    <t>Hogar de Niños María Luisa</t>
+  </si>
+  <si>
+    <t>Villa Ballester, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f3c4bc613966489d9037c022bdbef76e-psicologa-institucional-hogar-adolescentes-es-requisito-viva-en-zona-excluyente-hogar-de-ninos-maria-luisa-villa-ballester</t>
+  </si>
+  <si>
     <t>Public Health Director in beautiful Belize</t>
   </si>
   <si>
@@ -1885,9 +2242,6 @@
     <t>Green City Force</t>
   </si>
   <si>
-    <t>New York, NY</t>
-  </si>
-  <si>
     <t>USD 45000.00 - 55000.00/year</t>
   </si>
   <si>
@@ -1903,15 +2257,48 @@
     <t>School's Out Washington</t>
   </si>
   <si>
-    <t>Seattle, Washington</t>
-  </si>
-  <si>
     <t>USD 67800.00 - 81400.00/year</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/13d1eae1771e43c78c40b36eceea1ea8-refugee-school-impact-program-manager-schools-out-washington-seattle</t>
   </si>
   <si>
+    <t>Regional Outreach and Education Manager- NW Region</t>
+  </si>
+  <si>
+    <t>Intertribal Agriculture Council</t>
+  </si>
+  <si>
+    <t>Remote (Montana)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 81000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/17959c5dfa8b4a6290525fcd58e95495-regional-outreach-and-education-manager-nw-region-intertribal-agriculture-council-billings</t>
+  </si>
+  <si>
+    <t>Regional Outreach and Education Manager- SW Region</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f4e8ff708ee4be28c34081b51eb4e7f-regional-outreach-and-education-manager-sw-region-intertribal-agriculture-council-billings</t>
+  </si>
+  <si>
+    <t>Retail Associate</t>
+  </si>
+  <si>
+    <t>826 Valencia</t>
+  </si>
+  <si>
+    <t>USD 21.50 - 21.50/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dfc3d1cd83d641bfb89abc07880a73bd-retail-associate-826-valencia-san-francisco</t>
+  </si>
+  <si>
     <t>Safe House Program Assistant - (FT and PT)</t>
   </si>
   <si>
@@ -2017,6 +2404,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/72adaa05f40c419297a2339efd1055d3-senior-manager-qualitative-evaluation-and-insights-constructive-dialogue-institute-new-york</t>
   </si>
   <si>
+    <t>Senior Operations Manager, Prevention Pillar</t>
+  </si>
+  <si>
+    <t>Better Angels</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50c7ede4f52f43c2a71a1b8dacb00240-senior-operations-manager-prevention-pillar-better-angels-los-angeles</t>
+  </si>
+  <si>
     <t>Senior Paralegal</t>
   </si>
   <si>
@@ -2095,6 +2494,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/65cd42435550441b9471fa485740d195-speech-language-pathologist-volunteer-hillside-health-care-eldridgeville</t>
   </si>
   <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Legal Services for Prisoners with Children</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Prison Reform, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0250696e777049f58d1d0ea681413cdf-staff-attorney-legal-services-for-prisoners-with-children-oakland</t>
+  </si>
+  <si>
     <t>Staff Attorney - Workers' Rights</t>
   </si>
   <si>
@@ -2122,9 +2539,6 @@
     <t>Bolingbrook, Illinois</t>
   </si>
   <si>
-    <t>USD 85000.00 - 95000.00/year</t>
-  </si>
-  <si>
     <t>Immigrants Or Refugees, Legal Assistance</t>
   </si>
   <si>
@@ -2182,6 +2596,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/afd3cd0f384847869d7254c20ab4b528-summer-fellowship-education-pioneers-inc-dallas</t>
   </si>
   <si>
+    <t>Sunday Morning Nursery Teacher</t>
+  </si>
+  <si>
+    <t>First Parish in Cambridge, Unitarian Universalist</t>
+  </si>
+  <si>
+    <t>Cambridge, MA</t>
+  </si>
+  <si>
+    <t>USD 28.50 - 28.50/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/447f96b4468e4dedac3f12bb92829ee0-sunday-morning-nursery-teacher-first-parish-in-cambridge-unitarian-universalist-cambridge</t>
+  </si>
+  <si>
+    <t>Supervisión de innovación de Trabajadoras Comunitarias de Salud (enfoque en Atención Clínica)</t>
+  </si>
+  <si>
+    <t>Compañeros En Salud</t>
+  </si>
+  <si>
+    <t>Ángel Albino Corzo, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>MXN 21000.00 - 21000.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8602f282c28346eba3af64e73f31b20d-supervision-de-innovacion-de-trabajadoras-comunitarias-de-salud-enfoque-en-atencion-clinica-companeros-en-salud-angel-albino-corzo</t>
+  </si>
+  <si>
     <t>Teaching Artists - Dance &amp; Music</t>
   </si>
   <si>
@@ -2192,6 +2642,27 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/426713d96460461cac134cd66c56bfb1-teaching-artists-dance-music-marquis-studios-new-york</t>
+  </si>
+  <si>
+    <t>The Opportunity Network Director of People and Culture</t>
+  </si>
+  <si>
+    <t>Positively Partners</t>
+  </si>
+  <si>
+    <t>USD 118000.00 - 118000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/8e6a698c4951405490a03a6923389a78-the-opportunity-network-director-of-people-and-culture-positively-partners-boston</t>
+  </si>
+  <si>
+    <t>Visa Services &amp; Member Advisor</t>
+  </si>
+  <si>
+    <t>Arts Music, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1926a1f4f3fc4bc8b70a956456ad5125-visa-services-member-advisor-fractured-atlas-new-york</t>
   </si>
   <si>
     <t>Youth Counselor (Residential Services) (Full Time and Part-Time Shifts available)</t>
@@ -3638,7 +4109,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3696,17 +4167,41 @@
       <c r="F2" t="s">
         <v>232</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="H2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>234</v>
+      </c>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G3" t="s">
+        <v>239</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3715,7 +4210,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3756,2443 +4251,3202 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
         <v>236</v>
       </c>
-      <c r="C2" t="s">
-        <v>229</v>
-      </c>
       <c r="D2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" t="s">
         <v>236</v>
       </c>
-      <c r="C4" t="s">
-        <v>229</v>
-      </c>
       <c r="D4" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E4" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="F4" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F5" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C6" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D6" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F6" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B7" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C7" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D7" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F7" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B8" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C8" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D8" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="F8" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B9" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C9" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E9" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F9" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B10" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D10" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F10" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B11" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C11" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D11" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F11" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B12" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C12" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D12" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F12" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B13" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C13" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D13" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F13" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B14" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C14" t="s">
+        <v>289</v>
+      </c>
+      <c r="D14" t="s">
         <v>283</v>
       </c>
-      <c r="D14" t="s">
-        <v>277</v>
-      </c>
       <c r="E14" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F14" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B15" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C15" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D15" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F15" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C16" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D16" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="F16" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B17" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C17" t="s">
-        <v>283</v>
+        <v>325</v>
       </c>
       <c r="D17" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="F17" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B18" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C18" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F18" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B19" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C19" t="s">
-        <v>329</v>
+        <v>289</v>
       </c>
       <c r="D19" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E19" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F19" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B20" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C20" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D20" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F20" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B21" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C21" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F21" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B22" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C22" t="s">
-        <v>229</v>
+        <v>353</v>
       </c>
       <c r="D22" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F22" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B23" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C23" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="D23" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E23" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F23" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B24" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C24" t="s">
-        <v>357</v>
+        <v>236</v>
       </c>
       <c r="D24" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E24" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="F24" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="B25" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="C25" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="D25" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="F25" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B26" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="C26" t="s">
-        <v>365</v>
+        <v>236</v>
       </c>
       <c r="D26" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="F26" t="s">
-        <v>367</v>
+        <v>267</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B27" t="s">
-        <v>297</v>
+        <v>378</v>
       </c>
       <c r="C27" t="s">
-        <v>298</v>
+        <v>379</v>
       </c>
       <c r="D27" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>370</v>
+        <v>331</v>
       </c>
       <c r="F27" t="s">
-        <v>261</v>
+        <v>380</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B28" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C28" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="D28" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="F28" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B29" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C29" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="D29" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F29" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B30" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>392</v>
       </c>
       <c r="D30" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="F30" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="B31" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="C31" t="s">
-        <v>229</v>
+        <v>304</v>
       </c>
       <c r="D31" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>249</v>
+        <v>397</v>
       </c>
       <c r="F31" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B32" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="C32" t="s">
-        <v>229</v>
+        <v>401</v>
       </c>
       <c r="D32" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F32" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="B33" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="C33" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="D33" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F33" t="s">
-        <v>294</v>
+        <v>409</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="B34" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="C34" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="D34" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="F34" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>416</v>
+      </c>
+      <c r="B35" t="s">
+        <v>412</v>
+      </c>
+      <c r="C35" t="s">
+        <v>265</v>
+      </c>
+      <c r="D35" t="s">
+        <v>243</v>
+      </c>
+      <c r="E35" t="s">
+        <v>414</v>
+      </c>
+      <c r="F35" t="s">
         <v>403</v>
       </c>
-      <c r="B35" t="s">
-        <v>404</v>
-      </c>
-      <c r="C35" t="s">
-        <v>405</v>
-      </c>
-      <c r="D35" t="s">
-        <v>237</v>
-      </c>
-      <c r="E35" t="s">
-        <v>406</v>
-      </c>
-      <c r="F35" t="s">
-        <v>407</v>
-      </c>
       <c r="H35" s="2" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B36" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C36" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="D36" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E36" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="F36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="B37" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="C37" t="s">
-        <v>416</v>
+        <v>289</v>
       </c>
       <c r="D37" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
       <c r="E37" t="s">
-        <v>293</v>
+        <v>425</v>
       </c>
       <c r="F37" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B38" t="s">
-        <v>420</v>
+        <v>242</v>
       </c>
       <c r="C38" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="D38" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>421</v>
+        <v>255</v>
       </c>
       <c r="F38" t="s">
-        <v>325</v>
+        <v>245</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="B39" t="s">
-        <v>275</v>
+        <v>431</v>
       </c>
       <c r="C39" t="s">
-        <v>276</v>
+        <v>236</v>
       </c>
       <c r="D39" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F39" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B40" t="s">
-        <v>275</v>
+        <v>436</v>
       </c>
       <c r="C40" t="s">
-        <v>276</v>
+        <v>437</v>
       </c>
       <c r="D40" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="F40" t="s">
-        <v>429</v>
+        <v>300</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B41" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C41" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="D41" t="s">
-        <v>434</v>
+        <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>261</v>
+        <v>442</v>
       </c>
       <c r="F41" t="s">
-        <v>261</v>
+        <v>443</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B42" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C42" t="s">
-        <v>438</v>
+        <v>265</v>
       </c>
       <c r="D42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>261</v>
+        <v>446</v>
       </c>
       <c r="F42" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B43" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C43" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D43" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="F43" t="s">
-        <v>261</v>
+        <v>453</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="B44" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="C44" t="s">
-        <v>335</v>
+        <v>457</v>
       </c>
       <c r="D44" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="F44" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B45" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="C45" t="s">
-        <v>229</v>
+        <v>289</v>
       </c>
       <c r="D45" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="F45" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>466</v>
       </c>
       <c r="B46" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="C46" t="s">
         <v>457</v>
       </c>
       <c r="D46" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>458</v>
+        <v>299</v>
       </c>
       <c r="F46" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="B47" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="C47" t="s">
-        <v>463</v>
+        <v>289</v>
       </c>
       <c r="D47" t="s">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="F47" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B48" t="s">
-        <v>467</v>
+        <v>281</v>
       </c>
       <c r="C48" t="s">
-        <v>468</v>
+        <v>282</v>
       </c>
       <c r="D48" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F48" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B49" t="s">
-        <v>356</v>
+        <v>281</v>
       </c>
       <c r="C49" t="s">
-        <v>473</v>
+        <v>282</v>
       </c>
       <c r="D49" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>358</v>
+        <v>479</v>
       </c>
       <c r="F49" t="s">
-        <v>359</v>
+        <v>480</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B50" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="C50" t="s">
-        <v>229</v>
+        <v>484</v>
       </c>
       <c r="D50" t="s">
-        <v>237</v>
+        <v>485</v>
       </c>
       <c r="E50" t="s">
-        <v>477</v>
+        <v>267</v>
       </c>
       <c r="F50" t="s">
-        <v>478</v>
+        <v>267</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="B51" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>489</v>
       </c>
       <c r="D51" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E51" t="s">
-        <v>481</v>
+        <v>267</v>
       </c>
       <c r="F51" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B52" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C52" t="s">
-        <v>485</v>
+        <v>379</v>
       </c>
       <c r="D52" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F52" t="s">
-        <v>487</v>
+        <v>267</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B53" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C53" t="s">
-        <v>229</v>
+        <v>347</v>
       </c>
       <c r="D53" t="s">
-        <v>434</v>
+        <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>347</v>
+        <v>497</v>
       </c>
       <c r="F53" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="B54" t="s">
-        <v>269</v>
+        <v>501</v>
       </c>
       <c r="C54" t="s">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="D54" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="F54" t="s">
-        <v>272</v>
+        <v>503</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="B55" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C55" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="D55" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="F55" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>502</v>
+        <v>93</v>
       </c>
       <c r="B56" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C56" t="s">
-        <v>335</v>
+        <v>512</v>
       </c>
       <c r="D56" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E56" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="F56" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>507</v>
+        <v>93</v>
       </c>
       <c r="B57" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="C57" t="s">
-        <v>335</v>
+        <v>517</v>
       </c>
       <c r="D57" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E57" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="F57" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>509</v>
+        <v>93</v>
       </c>
       <c r="B58" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
       <c r="C58" t="s">
-        <v>335</v>
+        <v>522</v>
       </c>
       <c r="D58" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F58" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="B59" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="C59" t="s">
-        <v>443</v>
+        <v>527</v>
       </c>
       <c r="D59" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
       <c r="E59" t="s">
-        <v>309</v>
+        <v>528</v>
       </c>
       <c r="F59" t="s">
-        <v>261</v>
+        <v>332</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="B60" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="C60" t="s">
-        <v>229</v>
+        <v>532</v>
       </c>
       <c r="D60" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="F60" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="B61" t="s">
-        <v>520</v>
+        <v>383</v>
       </c>
       <c r="C61" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="D61" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E61" t="s">
-        <v>522</v>
+        <v>385</v>
       </c>
       <c r="F61" t="s">
-        <v>523</v>
+        <v>386</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="B62" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="C62" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D62" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="F62" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="B63" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="C63" t="s">
-        <v>416</v>
+        <v>236</v>
       </c>
       <c r="D63" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="F63" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="B64" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="C64" t="s">
-        <v>537</v>
+        <v>265</v>
       </c>
       <c r="D64" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F64" t="s">
-        <v>539</v>
+        <v>337</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="B65" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="C65" t="s">
-        <v>443</v>
+        <v>554</v>
       </c>
       <c r="D65" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E65" t="s">
-        <v>336</v>
+        <v>555</v>
       </c>
       <c r="F65" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="B66" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="C66" t="s">
-        <v>283</v>
+        <v>560</v>
       </c>
       <c r="D66" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E66" t="s">
-        <v>309</v>
+        <v>561</v>
       </c>
       <c r="F66" t="s">
-        <v>261</v>
+        <v>480</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>547</v>
+        <v>562</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="B67" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="C67" t="s">
-        <v>550</v>
+        <v>236</v>
       </c>
       <c r="D67" t="s">
-        <v>237</v>
+        <v>485</v>
       </c>
       <c r="E67" t="s">
-        <v>261</v>
+        <v>365</v>
       </c>
       <c r="F67" t="s">
-        <v>429</v>
+        <v>565</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>551</v>
+        <v>566</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="B68" t="s">
-        <v>553</v>
+        <v>275</v>
       </c>
       <c r="C68" t="s">
-        <v>554</v>
+        <v>276</v>
       </c>
       <c r="D68" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="F68" t="s">
-        <v>556</v>
+        <v>278</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="B69" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="C69" t="s">
-        <v>416</v>
+        <v>572</v>
       </c>
       <c r="D69" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="F69" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="B70" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="C70" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="D70" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="F70" t="s">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="B71" t="s">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="C71" t="s">
-        <v>443</v>
+        <v>289</v>
       </c>
       <c r="D71" t="s">
-        <v>237</v>
+        <v>485</v>
       </c>
       <c r="E71" t="s">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="F71" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>572</v>
+        <v>585</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="B72" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="C72" t="s">
-        <v>575</v>
+        <v>347</v>
       </c>
       <c r="D72" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="F72" t="s">
-        <v>325</v>
+        <v>589</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="B73" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C73" t="s">
-        <v>580</v>
+        <v>347</v>
       </c>
       <c r="D73" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="F73" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="B74" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C74" t="s">
-        <v>580</v>
+        <v>347</v>
       </c>
       <c r="D74" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="F74" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="B75" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="C75" t="s">
-        <v>580</v>
+        <v>379</v>
       </c>
       <c r="D75" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E75" t="s">
-        <v>581</v>
+        <v>315</v>
       </c>
       <c r="F75" t="s">
-        <v>582</v>
+        <v>267</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="B76" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="C76" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D76" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E76" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="F76" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="B77" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="C77" t="s">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="D77" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E77" t="s">
-        <v>278</v>
+        <v>606</v>
       </c>
       <c r="F77" t="s">
-        <v>597</v>
+        <v>267</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="B78" t="s">
-        <v>553</v>
+        <v>609</v>
       </c>
       <c r="C78" t="s">
-        <v>554</v>
+        <v>610</v>
       </c>
       <c r="D78" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E78" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="F78" t="s">
-        <v>556</v>
+        <v>612</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="B79" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="C79" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="D79" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E79" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="F79" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="B80" t="s">
-        <v>608</v>
+        <v>378</v>
       </c>
       <c r="C80" t="s">
-        <v>609</v>
+        <v>457</v>
       </c>
       <c r="D80" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E80" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="F80" t="s">
-        <v>611</v>
+        <v>380</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="B81" t="s">
-        <v>252</v>
+        <v>623</v>
       </c>
       <c r="C81" t="s">
-        <v>229</v>
+        <v>624</v>
       </c>
       <c r="D81" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E81" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="F81" t="s">
-        <v>255</v>
+        <v>626</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="B82" t="s">
-        <v>520</v>
+        <v>629</v>
       </c>
       <c r="C82" t="s">
-        <v>617</v>
+        <v>379</v>
       </c>
       <c r="D82" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E82" t="s">
-        <v>618</v>
+        <v>348</v>
       </c>
       <c r="F82" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="B83" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="C83" t="s">
-        <v>623</v>
+        <v>289</v>
       </c>
       <c r="D83" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E83" t="s">
-        <v>624</v>
+        <v>315</v>
       </c>
       <c r="F83" t="s">
-        <v>625</v>
+        <v>267</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="B84" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="C84" t="s">
-        <v>629</v>
+        <v>413</v>
       </c>
       <c r="D84" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E84" t="s">
-        <v>630</v>
+        <v>371</v>
       </c>
       <c r="F84" t="s">
-        <v>261</v>
+        <v>636</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="B85" t="s">
-        <v>484</v>
+        <v>639</v>
       </c>
       <c r="C85" t="s">
-        <v>485</v>
+        <v>640</v>
       </c>
       <c r="D85" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E85" t="s">
-        <v>633</v>
+        <v>267</v>
       </c>
       <c r="F85" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="B86" t="s">
-        <v>484</v>
+        <v>643</v>
       </c>
       <c r="C86" t="s">
-        <v>485</v>
+        <v>265</v>
       </c>
       <c r="D86" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E86" t="s">
-        <v>636</v>
+        <v>360</v>
       </c>
       <c r="F86" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="B87" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="C87" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="D87" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E87" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="F87" t="s">
-        <v>325</v>
+        <v>650</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="B88" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="C88" t="s">
-        <v>646</v>
+        <v>457</v>
       </c>
       <c r="D88" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E88" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="F88" t="s">
-        <v>261</v>
+        <v>655</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="B89" t="s">
-        <v>622</v>
+        <v>658</v>
       </c>
       <c r="C89" t="s">
-        <v>283</v>
+        <v>659</v>
       </c>
       <c r="D89" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E89" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="F89" t="s">
-        <v>625</v>
+        <v>661</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="B90" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="C90" t="s">
-        <v>229</v>
+        <v>665</v>
       </c>
       <c r="D90" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E90" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="F90" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="B91" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="C91" t="s">
-        <v>659</v>
+        <v>379</v>
       </c>
       <c r="D91" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E91" t="s">
-        <v>499</v>
+        <v>244</v>
       </c>
       <c r="F91" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>661</v>
+        <v>672</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>662</v>
+        <v>673</v>
       </c>
       <c r="B92" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="C92" t="s">
-        <v>229</v>
+        <v>675</v>
       </c>
       <c r="D92" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E92" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="F92" t="s">
-        <v>665</v>
+        <v>337</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>666</v>
+        <v>677</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="B93" t="s">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="C93" t="s">
-        <v>380</v>
+        <v>680</v>
       </c>
       <c r="D93" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E93" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="F93" t="s">
-        <v>670</v>
+        <v>636</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="B94" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C94" t="s">
-        <v>443</v>
+        <v>680</v>
       </c>
       <c r="D94" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E94" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="F94" t="s">
-        <v>325</v>
+        <v>684</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="B95" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C95" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D95" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E95" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="F95" t="s">
-        <v>660</v>
+        <v>636</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="B96" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="C96" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="D96" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E96" t="s">
-        <v>683</v>
+        <v>508</v>
       </c>
       <c r="F96" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>227</v>
+        <v>692</v>
       </c>
       <c r="B97" t="s">
-        <v>228</v>
+        <v>693</v>
       </c>
       <c r="C97" t="s">
-        <v>229</v>
+        <v>694</v>
       </c>
       <c r="D97" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E97" t="s">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="F97" t="s">
-        <v>533</v>
-      </c>
-      <c r="G97" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="B98" t="s">
-        <v>520</v>
+        <v>647</v>
       </c>
       <c r="C98" t="s">
-        <v>689</v>
+        <v>648</v>
       </c>
       <c r="D98" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E98" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="F98" t="s">
-        <v>691</v>
+        <v>650</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="B99" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="C99" t="s">
-        <v>695</v>
+        <v>289</v>
       </c>
       <c r="D99" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E99" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="F99" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="B100" t="s">
-        <v>700</v>
+        <v>559</v>
       </c>
       <c r="C100" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="D100" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E100" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="F100" t="s">
-        <v>703</v>
+        <v>480</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B101" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C101" t="s">
-        <v>443</v>
+        <v>711</v>
       </c>
       <c r="D101" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E101" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="F101" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="B102" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="C102" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="D102" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E102" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="F102" t="s">
-        <v>582</v>
+        <v>719</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="B103" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="C103" t="s">
-        <v>380</v>
+        <v>723</v>
       </c>
       <c r="D103" t="s">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="E103" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="F103" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="B104" t="s">
-        <v>716</v>
+        <v>258</v>
       </c>
       <c r="C104" t="s">
-        <v>720</v>
+        <v>236</v>
       </c>
       <c r="D104" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="E104" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="F104" t="s">
-        <v>718</v>
+        <v>261</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="B105" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="C105" t="s">
-        <v>283</v>
+        <v>732</v>
       </c>
       <c r="D105" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E105" t="s">
-        <v>724</v>
+        <v>267</v>
       </c>
       <c r="F105" t="s">
-        <v>660</v>
+        <v>733</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>725</v>
+        <v>734</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>726</v>
+        <v>735</v>
       </c>
       <c r="B106" t="s">
-        <v>727</v>
+        <v>609</v>
       </c>
       <c r="C106" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="D106" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E106" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="F106" t="s">
-        <v>449</v>
+        <v>738</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="B107" t="s">
-        <v>711</v>
+        <v>741</v>
       </c>
       <c r="C107" t="s">
-        <v>732</v>
+        <v>401</v>
       </c>
       <c r="D107" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E107" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="F107" t="s">
-        <v>449</v>
+        <v>743</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>734</v>
+        <v>744</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>745</v>
+      </c>
+      <c r="B108" t="s">
+        <v>746</v>
+      </c>
+      <c r="C108" t="s">
+        <v>706</v>
+      </c>
+      <c r="D108" t="s">
+        <v>243</v>
+      </c>
+      <c r="E108" t="s">
+        <v>747</v>
+      </c>
+      <c r="F108" t="s">
+        <v>267</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>749</v>
+      </c>
+      <c r="B109" t="s">
+        <v>750</v>
+      </c>
+      <c r="C109" t="s">
+        <v>751</v>
+      </c>
+      <c r="D109" t="s">
+        <v>243</v>
+      </c>
+      <c r="E109" t="s">
+        <v>752</v>
+      </c>
+      <c r="F109" t="s">
+        <v>753</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>755</v>
+      </c>
+      <c r="B110" t="s">
+        <v>750</v>
+      </c>
+      <c r="C110" t="s">
+        <v>751</v>
+      </c>
+      <c r="D110" t="s">
+        <v>243</v>
+      </c>
+      <c r="E110" t="s">
+        <v>752</v>
+      </c>
+      <c r="F110" t="s">
+        <v>753</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>757</v>
+      </c>
+      <c r="B111" t="s">
+        <v>758</v>
+      </c>
+      <c r="C111" t="s">
+        <v>413</v>
+      </c>
+      <c r="D111" t="s">
+        <v>250</v>
+      </c>
+      <c r="E111" t="s">
+        <v>759</v>
+      </c>
+      <c r="F111" t="s">
+        <v>403</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>761</v>
+      </c>
+      <c r="B112" t="s">
+        <v>553</v>
+      </c>
+      <c r="C112" t="s">
+        <v>554</v>
+      </c>
+      <c r="D112" t="s">
+        <v>243</v>
+      </c>
+      <c r="E112" t="s">
+        <v>762</v>
+      </c>
+      <c r="F112" t="s">
+        <v>556</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>764</v>
+      </c>
+      <c r="B113" t="s">
+        <v>553</v>
+      </c>
+      <c r="C113" t="s">
+        <v>554</v>
+      </c>
+      <c r="D113" t="s">
+        <v>243</v>
+      </c>
+      <c r="E113" t="s">
+        <v>765</v>
+      </c>
+      <c r="F113" t="s">
+        <v>766</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>768</v>
+      </c>
+      <c r="B114" t="s">
+        <v>769</v>
+      </c>
+      <c r="C114" t="s">
+        <v>770</v>
+      </c>
+      <c r="D114" t="s">
+        <v>243</v>
+      </c>
+      <c r="E114" t="s">
+        <v>771</v>
+      </c>
+      <c r="F114" t="s">
+        <v>337</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>773</v>
+      </c>
+      <c r="B115" t="s">
+        <v>774</v>
+      </c>
+      <c r="C115" t="s">
+        <v>775</v>
+      </c>
+      <c r="D115" t="s">
+        <v>243</v>
+      </c>
+      <c r="E115" t="s">
+        <v>776</v>
+      </c>
+      <c r="F115" t="s">
+        <v>267</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>778</v>
+      </c>
+      <c r="B116" t="s">
+        <v>741</v>
+      </c>
+      <c r="C116" t="s">
+        <v>289</v>
+      </c>
+      <c r="D116" t="s">
+        <v>243</v>
+      </c>
+      <c r="E116" t="s">
+        <v>779</v>
+      </c>
+      <c r="F116" t="s">
+        <v>743</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>781</v>
+      </c>
+      <c r="B117" t="s">
+        <v>782</v>
+      </c>
+      <c r="C117" t="s">
+        <v>236</v>
+      </c>
+      <c r="D117" t="s">
+        <v>243</v>
+      </c>
+      <c r="E117" t="s">
+        <v>783</v>
+      </c>
+      <c r="F117" t="s">
+        <v>784</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>786</v>
+      </c>
+      <c r="B118" t="s">
+        <v>787</v>
+      </c>
+      <c r="C118" t="s">
+        <v>788</v>
+      </c>
+      <c r="D118" t="s">
+        <v>243</v>
+      </c>
+      <c r="E118" t="s">
+        <v>579</v>
+      </c>
+      <c r="F118" t="s">
+        <v>789</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>791</v>
+      </c>
+      <c r="B119" t="s">
+        <v>792</v>
+      </c>
+      <c r="C119" t="s">
+        <v>236</v>
+      </c>
+      <c r="D119" t="s">
+        <v>243</v>
+      </c>
+      <c r="E119" t="s">
+        <v>793</v>
+      </c>
+      <c r="F119" t="s">
+        <v>794</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>796</v>
+      </c>
+      <c r="B120" t="s">
+        <v>797</v>
+      </c>
+      <c r="C120" t="s">
+        <v>265</v>
+      </c>
+      <c r="D120" t="s">
+        <v>243</v>
+      </c>
+      <c r="E120" t="s">
+        <v>414</v>
+      </c>
+      <c r="F120" t="s">
+        <v>798</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>800</v>
+      </c>
+      <c r="B121" t="s">
+        <v>801</v>
+      </c>
+      <c r="C121" t="s">
+        <v>413</v>
+      </c>
+      <c r="D121" t="s">
+        <v>243</v>
+      </c>
+      <c r="E121" t="s">
+        <v>802</v>
+      </c>
+      <c r="F121" t="s">
+        <v>803</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>805</v>
+      </c>
+      <c r="B122" t="s">
+        <v>806</v>
+      </c>
+      <c r="C122" t="s">
+        <v>379</v>
+      </c>
+      <c r="D122" t="s">
+        <v>243</v>
+      </c>
+      <c r="E122" t="s">
+        <v>807</v>
+      </c>
+      <c r="F122" t="s">
+        <v>337</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>809</v>
+      </c>
+      <c r="B123" t="s">
+        <v>810</v>
+      </c>
+      <c r="C123" t="s">
+        <v>811</v>
+      </c>
+      <c r="D123" t="s">
+        <v>250</v>
+      </c>
+      <c r="E123" t="s">
+        <v>812</v>
+      </c>
+      <c r="F123" t="s">
+        <v>789</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>814</v>
+      </c>
+      <c r="B124" t="s">
+        <v>815</v>
+      </c>
+      <c r="C124" t="s">
+        <v>289</v>
+      </c>
+      <c r="D124" t="s">
+        <v>243</v>
+      </c>
+      <c r="E124" t="s">
+        <v>816</v>
+      </c>
+      <c r="F124" t="s">
+        <v>817</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>234</v>
+      </c>
+      <c r="B125" t="s">
+        <v>235</v>
+      </c>
+      <c r="C125" t="s">
+        <v>236</v>
+      </c>
+      <c r="D125" t="s">
+        <v>243</v>
+      </c>
+      <c r="E125" t="s">
+        <v>244</v>
+      </c>
+      <c r="F125" t="s">
+        <v>380</v>
+      </c>
+      <c r="G125" t="s">
+        <v>819</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>821</v>
+      </c>
+      <c r="B126" t="s">
+        <v>609</v>
+      </c>
+      <c r="C126" t="s">
+        <v>822</v>
+      </c>
+      <c r="D126" t="s">
+        <v>243</v>
+      </c>
+      <c r="E126" t="s">
+        <v>823</v>
+      </c>
+      <c r="F126" t="s">
+        <v>824</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>826</v>
+      </c>
+      <c r="B127" t="s">
+        <v>827</v>
+      </c>
+      <c r="C127" t="s">
+        <v>828</v>
+      </c>
+      <c r="D127" t="s">
+        <v>243</v>
+      </c>
+      <c r="E127" t="s">
+        <v>829</v>
+      </c>
+      <c r="F127" t="s">
+        <v>830</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>832</v>
+      </c>
+      <c r="B128" t="s">
+        <v>833</v>
+      </c>
+      <c r="C128" t="s">
+        <v>834</v>
+      </c>
+      <c r="D128" t="s">
+        <v>243</v>
+      </c>
+      <c r="E128" t="s">
+        <v>835</v>
+      </c>
+      <c r="F128" t="s">
+        <v>836</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>838</v>
+      </c>
+      <c r="B129" t="s">
+        <v>839</v>
+      </c>
+      <c r="C129" t="s">
+        <v>840</v>
+      </c>
+      <c r="D129" t="s">
+        <v>243</v>
+      </c>
+      <c r="E129" t="s">
+        <v>829</v>
+      </c>
+      <c r="F129" t="s">
+        <v>841</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>843</v>
+      </c>
+      <c r="B130" t="s">
+        <v>844</v>
+      </c>
+      <c r="C130" t="s">
+        <v>379</v>
+      </c>
+      <c r="D130" t="s">
+        <v>243</v>
+      </c>
+      <c r="E130" t="s">
+        <v>845</v>
+      </c>
+      <c r="F130" t="s">
+        <v>846</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>848</v>
+      </c>
+      <c r="B131" t="s">
+        <v>849</v>
+      </c>
+      <c r="C131" t="s">
+        <v>850</v>
+      </c>
+      <c r="D131" t="s">
+        <v>243</v>
+      </c>
+      <c r="E131" t="s">
+        <v>851</v>
+      </c>
+      <c r="F131" t="s">
+        <v>636</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>853</v>
+      </c>
+      <c r="B132" t="s">
+        <v>854</v>
+      </c>
+      <c r="C132" t="s">
+        <v>413</v>
+      </c>
+      <c r="D132" t="s">
+        <v>283</v>
+      </c>
+      <c r="E132" t="s">
+        <v>855</v>
+      </c>
+      <c r="F132" t="s">
+        <v>856</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>853</v>
+      </c>
+      <c r="B133" t="s">
+        <v>854</v>
+      </c>
+      <c r="C133" t="s">
+        <v>858</v>
+      </c>
+      <c r="D133" t="s">
+        <v>283</v>
+      </c>
+      <c r="E133" t="s">
+        <v>855</v>
+      </c>
+      <c r="F133" t="s">
+        <v>856</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>860</v>
+      </c>
+      <c r="B134" t="s">
+        <v>861</v>
+      </c>
+      <c r="C134" t="s">
+        <v>862</v>
+      </c>
+      <c r="D134" t="s">
+        <v>250</v>
+      </c>
+      <c r="E134" t="s">
+        <v>863</v>
+      </c>
+      <c r="F134" t="s">
+        <v>864</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>866</v>
+      </c>
+      <c r="B135" t="s">
+        <v>867</v>
+      </c>
+      <c r="C135" t="s">
+        <v>868</v>
+      </c>
+      <c r="D135" t="s">
+        <v>283</v>
+      </c>
+      <c r="E135" t="s">
+        <v>869</v>
+      </c>
+      <c r="F135" t="s">
+        <v>870</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>872</v>
+      </c>
+      <c r="B136" t="s">
+        <v>873</v>
+      </c>
+      <c r="C136" t="s">
+        <v>289</v>
+      </c>
+      <c r="D136" t="s">
+        <v>250</v>
+      </c>
+      <c r="E136" t="s">
+        <v>874</v>
+      </c>
+      <c r="F136" t="s">
+        <v>789</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>876</v>
+      </c>
+      <c r="B137" t="s">
+        <v>877</v>
+      </c>
+      <c r="C137" t="s">
+        <v>236</v>
+      </c>
+      <c r="D137" t="s">
+        <v>243</v>
+      </c>
+      <c r="E137" t="s">
+        <v>878</v>
+      </c>
+      <c r="F137" t="s">
+        <v>337</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>880</v>
+      </c>
+      <c r="B138" t="s">
+        <v>540</v>
+      </c>
+      <c r="C138" t="s">
+        <v>236</v>
+      </c>
+      <c r="D138" t="s">
+        <v>243</v>
+      </c>
+      <c r="E138" t="s">
+        <v>541</v>
+      </c>
+      <c r="F138" t="s">
+        <v>881</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>883</v>
+      </c>
+      <c r="B139" t="s">
+        <v>884</v>
+      </c>
+      <c r="C139" t="s">
+        <v>885</v>
+      </c>
+      <c r="D139" t="s">
+        <v>243</v>
+      </c>
+      <c r="E139" t="s">
+        <v>886</v>
+      </c>
+      <c r="F139" t="s">
+        <v>498</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>888</v>
+      </c>
+      <c r="B140" t="s">
+        <v>849</v>
+      </c>
+      <c r="C140" t="s">
+        <v>889</v>
+      </c>
+      <c r="D140" t="s">
+        <v>243</v>
+      </c>
+      <c r="E140" t="s">
+        <v>890</v>
+      </c>
+      <c r="F140" t="s">
+        <v>498</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>891</v>
       </c>
     </row>
   </sheetData>
@@ -6304,6 +7558,39 @@
     <hyperlink ref="H105" r:id="rId104"/>
     <hyperlink ref="H106" r:id="rId105"/>
     <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-07.xlsx
+++ b/docs/xlsx/jobs-2026-10-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="896">
   <si>
     <t>Title</t>
   </si>
@@ -1789,16 +1789,28 @@
     <t>https://www.idealist.org/en/nonprofit-job/cc84eabe36f74e24bac02b8c3dc6f981-manager-of-learning-and-development-paul-m-angell-family-foundation-pmaff-chicago</t>
   </si>
   <si>
+    <t>Paul Angell Foundation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc84eabe36f74e24bac02b8c3dc6f981-manager-of-learning-and-development-paul-angell-foundation-chicago</t>
+  </si>
+  <si>
     <t>Manager of Program Initiatives</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/d390d095c8664d5bb49fc35431d6a83e-manager-of-program-initiatives-paul-m-angell-family-foundation-pmaff-chicago</t>
   </si>
   <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d390d095c8664d5bb49fc35431d6a83e-manager-of-program-initiatives-paul-angell-foundation-chicago</t>
+  </si>
+  <si>
     <t>Manager of Talent Acquisition, 5-Year Term</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/7239b5dadaf14f1988e29619902280b2-manager-of-talent-acquisition-5-year-term-paul-m-angell-family-foundation-pmaff-chicago</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7239b5dadaf14f1988e29619902280b2-manager-of-talent-acquisition-5-year-term-paul-angell-foundation-chicago</t>
   </si>
   <si>
     <t>Manager, Partner Success (Full-Time Position, Hybrid)</t>
@@ -4210,7 +4222,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -5884,10 +5896,10 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>586</v>
+      </c>
+      <c r="B73" t="s">
         <v>591</v>
-      </c>
-      <c r="B73" t="s">
-        <v>587</v>
       </c>
       <c r="C73" t="s">
         <v>347</v>
@@ -5930,102 +5942,102 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>593</v>
+      </c>
+      <c r="B75" t="s">
+        <v>591</v>
+      </c>
+      <c r="C75" t="s">
+        <v>347</v>
+      </c>
+      <c r="D75" t="s">
+        <v>243</v>
+      </c>
+      <c r="E75" t="s">
+        <v>588</v>
+      </c>
+      <c r="F75" t="s">
+        <v>589</v>
+      </c>
+      <c r="H75" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="B75" t="s">
-        <v>596</v>
-      </c>
-      <c r="C75" t="s">
-        <v>379</v>
-      </c>
-      <c r="D75" t="s">
-        <v>243</v>
-      </c>
-      <c r="E75" t="s">
-        <v>315</v>
-      </c>
-      <c r="F75" t="s">
-        <v>267</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B76" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="C76" t="s">
-        <v>236</v>
+        <v>347</v>
       </c>
       <c r="D76" t="s">
         <v>243</v>
       </c>
       <c r="E76" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="F76" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="B77" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="C77" t="s">
-        <v>605</v>
+        <v>347</v>
       </c>
       <c r="D77" t="s">
         <v>243</v>
       </c>
       <c r="E77" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="F77" t="s">
-        <v>267</v>
+        <v>589</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="B78" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="C78" t="s">
-        <v>610</v>
+        <v>379</v>
       </c>
       <c r="D78" t="s">
         <v>243</v>
       </c>
       <c r="E78" t="s">
-        <v>611</v>
+        <v>315</v>
       </c>
       <c r="F78" t="s">
-        <v>612</v>
+        <v>267</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="B79" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="C79" t="s">
         <v>236</v>
@@ -6034,1419 +6046,1488 @@
         <v>243</v>
       </c>
       <c r="E79" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="F79" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="B80" t="s">
-        <v>378</v>
+        <v>608</v>
       </c>
       <c r="C80" t="s">
-        <v>457</v>
+        <v>609</v>
       </c>
       <c r="D80" t="s">
         <v>243</v>
       </c>
       <c r="E80" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="F80" t="s">
-        <v>380</v>
+        <v>267</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="B81" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="C81" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="D81" t="s">
         <v>243</v>
       </c>
       <c r="E81" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="F81" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="B82" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="C82" t="s">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="D82" t="s">
         <v>243</v>
       </c>
       <c r="E82" t="s">
-        <v>348</v>
+        <v>620</v>
       </c>
       <c r="F82" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="B83" t="s">
-        <v>633</v>
+        <v>378</v>
       </c>
       <c r="C83" t="s">
-        <v>289</v>
+        <v>457</v>
       </c>
       <c r="D83" t="s">
         <v>243</v>
       </c>
       <c r="E83" t="s">
-        <v>315</v>
+        <v>624</v>
       </c>
       <c r="F83" t="s">
-        <v>267</v>
+        <v>380</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="B84" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="C84" t="s">
-        <v>413</v>
+        <v>628</v>
       </c>
       <c r="D84" t="s">
         <v>243</v>
       </c>
       <c r="E84" t="s">
-        <v>371</v>
+        <v>629</v>
       </c>
       <c r="F84" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="B85" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C85" t="s">
-        <v>640</v>
+        <v>379</v>
       </c>
       <c r="D85" t="s">
         <v>243</v>
       </c>
       <c r="E85" t="s">
-        <v>267</v>
+        <v>348</v>
       </c>
       <c r="F85" t="s">
-        <v>480</v>
+        <v>634</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B86" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C86" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="D86" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E86" t="s">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="F86" t="s">
-        <v>644</v>
+        <v>267</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="B87" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="C87" t="s">
-        <v>648</v>
+        <v>413</v>
       </c>
       <c r="D87" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E87" t="s">
-        <v>649</v>
+        <v>371</v>
       </c>
       <c r="F87" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="B88" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="C88" t="s">
-        <v>457</v>
+        <v>644</v>
       </c>
       <c r="D88" t="s">
         <v>243</v>
       </c>
       <c r="E88" t="s">
-        <v>654</v>
+        <v>267</v>
       </c>
       <c r="F88" t="s">
-        <v>655</v>
+        <v>480</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="B89" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="C89" t="s">
-        <v>659</v>
+        <v>265</v>
       </c>
       <c r="D89" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E89" t="s">
-        <v>660</v>
+        <v>360</v>
       </c>
       <c r="F89" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="B90" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="C90" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="D90" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E90" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="F90" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="B91" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="C91" t="s">
-        <v>379</v>
+        <v>457</v>
       </c>
       <c r="D91" t="s">
         <v>243</v>
       </c>
       <c r="E91" t="s">
-        <v>244</v>
+        <v>658</v>
       </c>
       <c r="F91" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="B92" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="C92" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="D92" t="s">
         <v>243</v>
       </c>
       <c r="E92" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="F92" t="s">
-        <v>337</v>
+        <v>665</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="B93" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="C93" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="D93" t="s">
         <v>243</v>
       </c>
       <c r="E93" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="F93" t="s">
-        <v>636</v>
+        <v>671</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="B94" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="C94" t="s">
-        <v>680</v>
+        <v>379</v>
       </c>
       <c r="D94" t="s">
         <v>243</v>
       </c>
       <c r="E94" t="s">
-        <v>681</v>
+        <v>244</v>
       </c>
       <c r="F94" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="B95" t="s">
+        <v>678</v>
+      </c>
+      <c r="C95" t="s">
         <v>679</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
+        <v>243</v>
+      </c>
+      <c r="E95" t="s">
         <v>680</v>
       </c>
-      <c r="D95" t="s">
-        <v>243</v>
-      </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
+        <v>337</v>
+      </c>
+      <c r="H95" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="F95" t="s">
-        <v>636</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="B96" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C96" t="s">
-        <v>236</v>
+        <v>684</v>
       </c>
       <c r="D96" t="s">
         <v>243</v>
       </c>
       <c r="E96" t="s">
-        <v>508</v>
+        <v>685</v>
       </c>
       <c r="F96" t="s">
-        <v>690</v>
+        <v>640</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="B97" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="C97" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="D97" t="s">
         <v>243</v>
       </c>
       <c r="E97" t="s">
-        <v>284</v>
+        <v>685</v>
       </c>
       <c r="F97" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="B98" t="s">
-        <v>647</v>
+        <v>683</v>
       </c>
       <c r="C98" t="s">
-        <v>648</v>
+        <v>684</v>
       </c>
       <c r="D98" t="s">
         <v>243</v>
       </c>
       <c r="E98" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="F98" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="B99" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="C99" t="s">
-        <v>289</v>
+        <v>236</v>
       </c>
       <c r="D99" t="s">
         <v>243</v>
       </c>
       <c r="E99" t="s">
-        <v>702</v>
+        <v>508</v>
       </c>
       <c r="F99" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="B100" t="s">
-        <v>559</v>
+        <v>697</v>
       </c>
       <c r="C100" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="D100" t="s">
         <v>243</v>
       </c>
       <c r="E100" t="s">
-        <v>707</v>
+        <v>284</v>
       </c>
       <c r="F100" t="s">
-        <v>480</v>
+        <v>699</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="B101" t="s">
-        <v>710</v>
+        <v>651</v>
       </c>
       <c r="C101" t="s">
-        <v>711</v>
+        <v>652</v>
       </c>
       <c r="D101" t="s">
         <v>243</v>
       </c>
       <c r="E101" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="F101" t="s">
-        <v>713</v>
+        <v>654</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="B102" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="C102" t="s">
-        <v>717</v>
+        <v>289</v>
       </c>
       <c r="D102" t="s">
         <v>243</v>
       </c>
       <c r="E102" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="F102" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="B103" t="s">
-        <v>722</v>
+        <v>559</v>
       </c>
       <c r="C103" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="D103" t="s">
         <v>243</v>
       </c>
       <c r="E103" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="F103" t="s">
-        <v>725</v>
+        <v>480</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="B104" t="s">
-        <v>258</v>
+        <v>714</v>
       </c>
       <c r="C104" t="s">
-        <v>236</v>
+        <v>715</v>
       </c>
       <c r="D104" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E104" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="F104" t="s">
-        <v>261</v>
+        <v>717</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="B105" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="C105" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="D105" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E105" t="s">
-        <v>267</v>
+        <v>722</v>
       </c>
       <c r="F105" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="B106" t="s">
-        <v>609</v>
+        <v>726</v>
       </c>
       <c r="C106" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="D106" t="s">
         <v>243</v>
       </c>
       <c r="E106" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="F106" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="B107" t="s">
-        <v>741</v>
+        <v>258</v>
       </c>
       <c r="C107" t="s">
-        <v>401</v>
+        <v>236</v>
       </c>
       <c r="D107" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E107" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="F107" t="s">
-        <v>743</v>
+        <v>261</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="B108" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="C108" t="s">
-        <v>706</v>
+        <v>736</v>
       </c>
       <c r="D108" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E108" t="s">
-        <v>747</v>
+        <v>267</v>
       </c>
       <c r="F108" t="s">
-        <v>267</v>
+        <v>737</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="B109" t="s">
-        <v>750</v>
+        <v>613</v>
       </c>
       <c r="C109" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="D109" t="s">
         <v>243</v>
       </c>
       <c r="E109" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="F109" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="B110" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="C110" t="s">
-        <v>751</v>
+        <v>401</v>
       </c>
       <c r="D110" t="s">
         <v>243</v>
       </c>
       <c r="E110" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="F110" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="B111" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="C111" t="s">
-        <v>413</v>
+        <v>710</v>
       </c>
       <c r="D111" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E111" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="F111" t="s">
-        <v>403</v>
+        <v>267</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="B112" t="s">
-        <v>553</v>
+        <v>754</v>
       </c>
       <c r="C112" t="s">
-        <v>554</v>
+        <v>755</v>
       </c>
       <c r="D112" t="s">
         <v>243</v>
       </c>
       <c r="E112" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="F112" t="s">
-        <v>556</v>
+        <v>757</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="B113" t="s">
-        <v>553</v>
+        <v>754</v>
       </c>
       <c r="C113" t="s">
-        <v>554</v>
+        <v>755</v>
       </c>
       <c r="D113" t="s">
         <v>243</v>
       </c>
       <c r="E113" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="F113" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="B114" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="C114" t="s">
-        <v>770</v>
+        <v>413</v>
       </c>
       <c r="D114" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E114" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="F114" t="s">
-        <v>337</v>
+        <v>403</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="B115" t="s">
-        <v>774</v>
+        <v>553</v>
       </c>
       <c r="C115" t="s">
-        <v>775</v>
+        <v>554</v>
       </c>
       <c r="D115" t="s">
         <v>243</v>
       </c>
       <c r="E115" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="F115" t="s">
-        <v>267</v>
+        <v>556</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="B116" t="s">
-        <v>741</v>
+        <v>553</v>
       </c>
       <c r="C116" t="s">
-        <v>289</v>
+        <v>554</v>
       </c>
       <c r="D116" t="s">
         <v>243</v>
       </c>
       <c r="E116" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="F116" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="B117" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="C117" t="s">
-        <v>236</v>
+        <v>774</v>
       </c>
       <c r="D117" t="s">
         <v>243</v>
       </c>
       <c r="E117" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="F117" t="s">
-        <v>784</v>
+        <v>337</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="B118" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="C118" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="D118" t="s">
         <v>243</v>
       </c>
       <c r="E118" t="s">
-        <v>579</v>
+        <v>780</v>
       </c>
       <c r="F118" t="s">
-        <v>789</v>
+        <v>267</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
       <c r="B119" t="s">
-        <v>792</v>
+        <v>745</v>
       </c>
       <c r="C119" t="s">
-        <v>236</v>
+        <v>289</v>
       </c>
       <c r="D119" t="s">
         <v>243</v>
       </c>
       <c r="E119" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="F119" t="s">
-        <v>794</v>
+        <v>747</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="B120" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="C120" t="s">
-        <v>265</v>
+        <v>236</v>
       </c>
       <c r="D120" t="s">
         <v>243</v>
       </c>
       <c r="E120" t="s">
-        <v>414</v>
+        <v>787</v>
       </c>
       <c r="F120" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="B121" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="C121" t="s">
-        <v>413</v>
+        <v>792</v>
       </c>
       <c r="D121" t="s">
         <v>243</v>
       </c>
       <c r="E121" t="s">
-        <v>802</v>
+        <v>579</v>
       </c>
       <c r="F121" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="B122" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="C122" t="s">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="D122" t="s">
         <v>243</v>
       </c>
       <c r="E122" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="F122" t="s">
-        <v>337</v>
+        <v>798</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="B123" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="C123" t="s">
-        <v>811</v>
+        <v>265</v>
       </c>
       <c r="D123" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E123" t="s">
-        <v>812</v>
+        <v>414</v>
       </c>
       <c r="F123" t="s">
-        <v>789</v>
+        <v>802</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="B124" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="C124" t="s">
-        <v>289</v>
+        <v>413</v>
       </c>
       <c r="D124" t="s">
         <v>243</v>
       </c>
       <c r="E124" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="F124" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>234</v>
+        <v>809</v>
       </c>
       <c r="B125" t="s">
-        <v>235</v>
+        <v>810</v>
       </c>
       <c r="C125" t="s">
-        <v>236</v>
+        <v>379</v>
       </c>
       <c r="D125" t="s">
         <v>243</v>
       </c>
       <c r="E125" t="s">
-        <v>244</v>
+        <v>811</v>
       </c>
       <c r="F125" t="s">
-        <v>380</v>
-      </c>
-      <c r="G125" t="s">
-        <v>819</v>
+        <v>337</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="B126" t="s">
-        <v>609</v>
+        <v>814</v>
       </c>
       <c r="C126" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="D126" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E126" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="F126" t="s">
-        <v>824</v>
+        <v>793</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="B127" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="C127" t="s">
-        <v>828</v>
+        <v>289</v>
       </c>
       <c r="D127" t="s">
         <v>243</v>
       </c>
       <c r="E127" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
       <c r="F127" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>832</v>
+        <v>234</v>
       </c>
       <c r="B128" t="s">
-        <v>833</v>
+        <v>235</v>
       </c>
       <c r="C128" t="s">
-        <v>834</v>
+        <v>236</v>
       </c>
       <c r="D128" t="s">
         <v>243</v>
       </c>
       <c r="E128" t="s">
-        <v>835</v>
+        <v>244</v>
       </c>
       <c r="F128" t="s">
-        <v>836</v>
+        <v>380</v>
+      </c>
+      <c r="G128" t="s">
+        <v>823</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="B129" t="s">
-        <v>839</v>
+        <v>613</v>
       </c>
       <c r="C129" t="s">
-        <v>840</v>
+        <v>826</v>
       </c>
       <c r="D129" t="s">
         <v>243</v>
       </c>
       <c r="E129" t="s">
+        <v>827</v>
+      </c>
+      <c r="F129" t="s">
+        <v>828</v>
+      </c>
+      <c r="H129" s="2" t="s">
         <v>829</v>
-      </c>
-      <c r="F129" t="s">
-        <v>841</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="B130" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
       <c r="C130" t="s">
-        <v>379</v>
+        <v>832</v>
       </c>
       <c r="D130" t="s">
         <v>243</v>
       </c>
       <c r="E130" t="s">
-        <v>845</v>
+        <v>833</v>
       </c>
       <c r="F130" t="s">
-        <v>846</v>
+        <v>834</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
       <c r="B131" t="s">
-        <v>849</v>
+        <v>837</v>
       </c>
       <c r="C131" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="D131" t="s">
         <v>243</v>
       </c>
       <c r="E131" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="F131" t="s">
-        <v>636</v>
+        <v>840</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>852</v>
+        <v>841</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>853</v>
+        <v>842</v>
       </c>
       <c r="B132" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="C132" t="s">
-        <v>413</v>
+        <v>844</v>
       </c>
       <c r="D132" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="E132" t="s">
-        <v>855</v>
+        <v>833</v>
       </c>
       <c r="F132" t="s">
-        <v>856</v>
+        <v>845</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>857</v>
+        <v>846</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="B133" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="C133" t="s">
-        <v>858</v>
+        <v>379</v>
       </c>
       <c r="D133" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="E133" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="F133" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="B134" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="C134" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="D134" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E134" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="F134" t="s">
-        <v>864</v>
+        <v>640</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
       <c r="B135" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="C135" t="s">
-        <v>868</v>
+        <v>413</v>
       </c>
       <c r="D135" t="s">
         <v>283</v>
       </c>
       <c r="E135" t="s">
-        <v>869</v>
+        <v>859</v>
       </c>
       <c r="F135" t="s">
-        <v>870</v>
+        <v>860</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>871</v>
+        <v>861</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>872</v>
+        <v>857</v>
       </c>
       <c r="B136" t="s">
-        <v>873</v>
+        <v>858</v>
       </c>
       <c r="C136" t="s">
-        <v>289</v>
+        <v>862</v>
       </c>
       <c r="D136" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="E136" t="s">
-        <v>874</v>
+        <v>859</v>
       </c>
       <c r="F136" t="s">
-        <v>789</v>
+        <v>860</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>875</v>
+        <v>863</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="B137" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
       <c r="C137" t="s">
-        <v>236</v>
+        <v>866</v>
       </c>
       <c r="D137" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E137" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="F137" t="s">
-        <v>337</v>
+        <v>868</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="B138" t="s">
-        <v>540</v>
+        <v>871</v>
       </c>
       <c r="C138" t="s">
-        <v>236</v>
+        <v>872</v>
       </c>
       <c r="D138" t="s">
-        <v>243</v>
+        <v>283</v>
       </c>
       <c r="E138" t="s">
-        <v>541</v>
+        <v>873</v>
       </c>
       <c r="F138" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="B139" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="C139" t="s">
-        <v>885</v>
+        <v>289</v>
       </c>
       <c r="D139" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E139" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="F139" t="s">
-        <v>498</v>
+        <v>793</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>880</v>
+      </c>
+      <c r="B140" t="s">
+        <v>881</v>
+      </c>
+      <c r="C140" t="s">
+        <v>236</v>
+      </c>
+      <c r="D140" t="s">
+        <v>243</v>
+      </c>
+      <c r="E140" t="s">
+        <v>882</v>
+      </c>
+      <c r="F140" t="s">
+        <v>337</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>884</v>
+      </c>
+      <c r="B141" t="s">
+        <v>540</v>
+      </c>
+      <c r="C141" t="s">
+        <v>236</v>
+      </c>
+      <c r="D141" t="s">
+        <v>243</v>
+      </c>
+      <c r="E141" t="s">
+        <v>541</v>
+      </c>
+      <c r="F141" t="s">
+        <v>885</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>887</v>
+      </c>
+      <c r="B142" t="s">
         <v>888</v>
       </c>
-      <c r="B140" t="s">
-        <v>849</v>
-      </c>
-      <c r="C140" t="s">
+      <c r="C142" t="s">
         <v>889</v>
       </c>
-      <c r="D140" t="s">
-        <v>243</v>
-      </c>
-      <c r="E140" t="s">
+      <c r="D142" t="s">
+        <v>243</v>
+      </c>
+      <c r="E142" t="s">
         <v>890</v>
       </c>
-      <c r="F140" t="s">
+      <c r="F142" t="s">
         <v>498</v>
       </c>
-      <c r="H140" s="2" t="s">
+      <c r="H142" s="2" t="s">
         <v>891</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>892</v>
+      </c>
+      <c r="B143" t="s">
+        <v>853</v>
+      </c>
+      <c r="C143" t="s">
+        <v>893</v>
+      </c>
+      <c r="D143" t="s">
+        <v>243</v>
+      </c>
+      <c r="E143" t="s">
+        <v>894</v>
+      </c>
+      <c r="F143" t="s">
+        <v>498</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>895</v>
       </c>
     </row>
   </sheetData>
@@ -7591,6 +7672,9 @@
     <hyperlink ref="H138" r:id="rId137"/>
     <hyperlink ref="H139" r:id="rId138"/>
     <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
